--- a/2025.xlsx
+++ b/2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.10\Assofrutti\MAGAZZINO\RACCOLTO 2025 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabriele/Desktop/Magazzino semilavorati/magazzino-assofrutti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4899F1-AC36-4AB0-9049-80D748A1C2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDF7B38-CEE6-7743-ACD9-9112022BBB4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="471" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="471" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BIOLOGICO" sheetId="3" r:id="rId1"/>
@@ -18,21 +18,10 @@
     <sheet name="CONVENZIONALE" sheetId="11" r:id="rId3"/>
     <sheet name="BIO BIOSUISSE" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1065,7 +1054,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1929,28 +1918,6 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1971,6 +1938,51 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1993,34 +2005,17 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2028,12 +2023,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2058,9 +2047,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2098,7 +2087,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2204,7 +2193,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2346,7 +2335,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2358,29 +2347,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" customWidth="1"/>
-    <col min="13" max="15" width="10.140625" customWidth="1"/>
-    <col min="16" max="16" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" customWidth="1"/>
+    <col min="13" max="15" width="10.1640625" customWidth="1"/>
+    <col min="16" max="16" width="7.83203125" customWidth="1"/>
     <col min="17" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" customWidth="1"/>
+    <col min="18" max="18" width="8.5" customWidth="1"/>
     <col min="19" max="19" width="8" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" ht="26" thickBot="1">
       <c r="A1" s="189" t="s">
         <v>0</v>
       </c>
@@ -2391,18 +2380,18 @@
       </c>
       <c r="E1" s="190"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="200" t="s">
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="201"/>
-    </row>
-    <row r="2" spans="1:21" ht="39" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="209"/>
+    </row>
+    <row r="2" spans="1:21" ht="33" thickTop="1">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -2465,7 +2454,7 @@
       </c>
       <c r="U2" s="138"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21">
       <c r="A3" s="81"/>
       <c r="B3" s="118"/>
       <c r="C3" s="45"/>
@@ -2491,7 +2480,7 @@
       <c r="T3" s="13"/>
       <c r="U3" s="119"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21">
       <c r="A4" s="81"/>
       <c r="B4" s="118"/>
       <c r="C4" s="45"/>
@@ -2517,7 +2506,7 @@
       <c r="T4" s="13"/>
       <c r="U4" s="119"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21">
       <c r="A5" s="81"/>
       <c r="B5" s="118"/>
       <c r="C5" s="45"/>
@@ -2543,7 +2532,7 @@
       <c r="T5" s="13"/>
       <c r="U5" s="119"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21">
       <c r="A6" s="19"/>
       <c r="B6" s="74"/>
       <c r="C6" s="96"/>
@@ -2568,7 +2557,7 @@
       <c r="T6" s="13"/>
       <c r="U6" s="119"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21">
       <c r="A7" s="19"/>
       <c r="B7" s="74"/>
       <c r="C7" s="96"/>
@@ -2591,7 +2580,7 @@
       <c r="T7" s="13"/>
       <c r="U7" s="119"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21">
       <c r="A8" s="112"/>
       <c r="B8" s="112"/>
       <c r="C8" s="99"/>
@@ -2614,7 +2603,7 @@
       <c r="T8" s="13"/>
       <c r="U8" s="119"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21">
       <c r="A9" s="112"/>
       <c r="B9" s="112"/>
       <c r="C9" s="99"/>
@@ -2637,7 +2626,7 @@
       <c r="T9" s="13"/>
       <c r="U9" s="119"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21">
       <c r="A10" s="113"/>
       <c r="B10" s="111"/>
       <c r="C10" s="70"/>
@@ -2687,7 +2676,7 @@
       <c r="T10" s="26"/>
       <c r="U10" s="119"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="A11" s="81" t="s">
         <v>79</v>
       </c>
@@ -2739,7 +2728,7 @@
       </c>
       <c r="U11" s="119"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21">
       <c r="A12" s="81" t="s">
         <v>79</v>
       </c>
@@ -2791,7 +2780,7 @@
       </c>
       <c r="U12" s="119"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="A13" s="81" t="s">
         <v>79</v>
       </c>
@@ -2843,7 +2832,7 @@
       </c>
       <c r="U13" s="119"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21">
       <c r="A14" s="81" t="s">
         <v>79</v>
       </c>
@@ -2895,7 +2884,7 @@
       </c>
       <c r="U14" s="119"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="A15" s="81" t="s">
         <v>79</v>
       </c>
@@ -2947,7 +2936,7 @@
       </c>
       <c r="U15" s="119"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="A16" s="81" t="s">
         <v>178</v>
       </c>
@@ -2999,7 +2988,7 @@
       </c>
       <c r="U16" s="119"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21">
       <c r="A17" s="81"/>
       <c r="B17" s="118"/>
       <c r="C17" s="45"/>
@@ -3025,7 +3014,7 @@
       <c r="T17" s="26"/>
       <c r="U17" s="119"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21">
       <c r="A18" s="114"/>
       <c r="B18" s="78"/>
       <c r="C18" s="30"/>
@@ -3050,7 +3039,7 @@
       <c r="T18" s="26"/>
       <c r="U18" s="119"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21">
       <c r="A19" s="114"/>
       <c r="B19" s="78"/>
       <c r="C19" s="30"/>
@@ -3073,7 +3062,7 @@
       <c r="T19" s="26"/>
       <c r="U19" s="119"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21">
       <c r="A20" s="114"/>
       <c r="B20" s="78"/>
       <c r="C20" s="30"/>
@@ -3102,7 +3091,7 @@
       <c r="T20" s="26"/>
       <c r="U20" s="119"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21">
       <c r="A21" s="114"/>
       <c r="B21" s="78"/>
       <c r="C21" s="30"/>
@@ -3125,7 +3114,7 @@
       <c r="T21" s="26"/>
       <c r="U21" s="119"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21">
       <c r="A22" s="114"/>
       <c r="B22" s="78"/>
       <c r="C22" s="30"/>
@@ -3148,7 +3137,7 @@
       <c r="T22" s="26"/>
       <c r="U22" s="119"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21">
       <c r="A23" s="114"/>
       <c r="B23" s="78"/>
       <c r="C23" s="78"/>
@@ -3171,7 +3160,7 @@
       <c r="T23" s="26"/>
       <c r="U23" s="119"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21">
       <c r="A24" s="70"/>
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
@@ -3221,7 +3210,7 @@
       <c r="T24" s="26"/>
       <c r="U24" s="119"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21">
       <c r="A25" s="81" t="s">
         <v>58</v>
       </c>
@@ -3273,7 +3262,7 @@
       </c>
       <c r="U25" s="119"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21">
       <c r="A26" s="81" t="s">
         <v>74</v>
       </c>
@@ -3325,7 +3314,7 @@
       </c>
       <c r="U26" s="119"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21">
       <c r="A27" s="81" t="s">
         <v>79</v>
       </c>
@@ -3377,7 +3366,7 @@
       </c>
       <c r="U27" s="119"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21">
       <c r="A28" s="81" t="s">
         <v>79</v>
       </c>
@@ -3429,7 +3418,7 @@
       </c>
       <c r="U28" s="119"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21">
       <c r="A29" s="81" t="s">
         <v>79</v>
       </c>
@@ -3481,7 +3470,7 @@
       </c>
       <c r="U29" s="119"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21">
       <c r="A30" s="81" t="s">
         <v>79</v>
       </c>
@@ -3533,7 +3522,7 @@
       </c>
       <c r="U30" s="119"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21">
       <c r="A31" s="81" t="s">
         <v>79</v>
       </c>
@@ -3585,7 +3574,7 @@
       </c>
       <c r="U31" s="119"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21">
       <c r="A32" s="81" t="s">
         <v>79</v>
       </c>
@@ -3637,7 +3626,7 @@
       </c>
       <c r="U32" s="119"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21">
       <c r="A33" s="81" t="s">
         <v>79</v>
       </c>
@@ -3689,7 +3678,7 @@
       </c>
       <c r="U33" s="119"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21">
       <c r="A34" s="81" t="s">
         <v>178</v>
       </c>
@@ -3741,7 +3730,7 @@
       </c>
       <c r="U34" s="119"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21">
       <c r="A35" s="81" t="s">
         <v>178</v>
       </c>
@@ -3793,7 +3782,7 @@
       </c>
       <c r="U35" s="119"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21">
       <c r="A36" s="174"/>
       <c r="B36" s="175"/>
       <c r="C36" s="176"/>
@@ -3819,7 +3808,7 @@
       <c r="T36" s="26"/>
       <c r="U36" s="119"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21">
       <c r="A37" s="81"/>
       <c r="B37" s="118"/>
       <c r="C37" s="45"/>
@@ -3845,7 +3834,7 @@
       <c r="T37" s="26"/>
       <c r="U37" s="119"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21">
       <c r="A38" s="34"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -3870,7 +3859,7 @@
       <c r="T38" s="26"/>
       <c r="U38" s="119"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21">
       <c r="A39" s="34"/>
       <c r="B39" s="35"/>
       <c r="C39" s="35"/>
@@ -3893,7 +3882,7 @@
       <c r="T39" s="26"/>
       <c r="U39" s="119"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21">
       <c r="A40" s="34"/>
       <c r="B40" s="35"/>
       <c r="C40" s="35"/>
@@ -3920,7 +3909,7 @@
       <c r="T40" s="26"/>
       <c r="U40" s="119"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21">
       <c r="A41" s="34"/>
       <c r="B41" s="35"/>
       <c r="C41" s="35"/>
@@ -3943,7 +3932,7 @@
       <c r="T41" s="26"/>
       <c r="U41" s="119"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21">
       <c r="A42" s="34"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -3966,7 +3955,7 @@
       <c r="T42" s="26"/>
       <c r="U42" s="119"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21">
       <c r="A43" s="34"/>
       <c r="B43" s="35"/>
       <c r="C43" s="35"/>
@@ -3989,7 +3978,7 @@
       <c r="T43" s="26"/>
       <c r="U43" s="119"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21">
       <c r="A44" s="34"/>
       <c r="B44" s="35"/>
       <c r="C44" s="80"/>
@@ -4012,7 +4001,7 @@
       <c r="T44" s="26"/>
       <c r="U44" s="119"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21">
       <c r="A45" s="70"/>
       <c r="B45" s="131"/>
       <c r="C45" s="70"/>
@@ -4062,7 +4051,7 @@
       <c r="T45" s="26"/>
       <c r="U45" s="119"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21">
       <c r="A46" s="81"/>
       <c r="B46" s="118"/>
       <c r="C46" s="45"/>
@@ -4088,7 +4077,7 @@
       <c r="T46" s="94"/>
       <c r="U46" s="123"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21">
       <c r="A47" s="124"/>
       <c r="B47" s="133"/>
       <c r="C47" s="125"/>
@@ -4114,7 +4103,7 @@
       <c r="T47" s="18"/>
       <c r="U47" s="122"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21">
       <c r="A48" s="127"/>
       <c r="B48" s="134"/>
       <c r="C48" s="125"/>
@@ -4140,7 +4129,7 @@
       <c r="T48" s="18"/>
       <c r="U48" s="123"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21">
       <c r="A49" s="128"/>
       <c r="B49" s="135"/>
       <c r="C49" s="129"/>
@@ -4190,7 +4179,7 @@
       <c r="T49" s="18"/>
       <c r="U49" s="123"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21">
       <c r="A50" s="128" t="s">
         <v>79</v>
       </c>
@@ -4242,7 +4231,7 @@
       </c>
       <c r="U50" s="123"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21">
       <c r="A51" s="128"/>
       <c r="B51" s="135"/>
       <c r="C51" s="129"/>
@@ -4268,7 +4257,7 @@
       <c r="T51" s="18"/>
       <c r="U51" s="123"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21">
       <c r="A52" s="128"/>
       <c r="B52" s="135"/>
       <c r="C52" s="129"/>
@@ -4294,7 +4283,7 @@
       <c r="T52" s="18"/>
       <c r="U52" s="123"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21">
       <c r="A53" s="128" t="s">
         <v>79</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="U53" s="123"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21">
       <c r="A54" s="128"/>
       <c r="B54" s="135"/>
       <c r="C54" s="129"/>
@@ -4372,7 +4361,7 @@
       <c r="T54" s="18"/>
       <c r="U54" s="123"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21">
       <c r="A55" s="70"/>
       <c r="B55" s="131"/>
       <c r="C55" s="70"/>
@@ -4422,7 +4411,7 @@
       <c r="T55" s="26"/>
       <c r="U55" s="111"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21">
       <c r="A56" s="70"/>
       <c r="B56" s="131"/>
       <c r="C56" s="81"/>
@@ -4445,7 +4434,7 @@
       <c r="T56" s="26"/>
       <c r="U56" s="111"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21">
       <c r="A57" s="70"/>
       <c r="B57" s="131"/>
       <c r="C57" s="70"/>
@@ -4468,14 +4457,14 @@
       <c r="T57" s="70"/>
       <c r="U57" s="111"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21">
       <c r="A58" s="70"/>
       <c r="B58" s="131"/>
       <c r="C58" s="70"/>
-      <c r="D58" s="202" t="s">
+      <c r="D58" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="203"/>
+      <c r="E58" s="214"/>
       <c r="F58" s="39">
         <f>SUM(F10,F24,F45,F49,F55)</f>
         <v>16018</v>
@@ -4516,7 +4505,7 @@
       <c r="T58" s="70"/>
       <c r="U58" s="111"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21">
       <c r="A59" s="111"/>
       <c r="B59" s="111"/>
       <c r="C59" s="111"/>
@@ -4539,7 +4528,7 @@
       <c r="T59" s="111"/>
       <c r="U59" s="111"/>
     </row>
-    <row r="60" spans="1:21" ht="18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="18">
       <c r="A60" s="111"/>
       <c r="B60" s="111"/>
       <c r="C60" s="111"/>
@@ -4567,7 +4556,7 @@
       <c r="T60" s="111"/>
       <c r="U60" s="111"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21">
       <c r="A61" s="111"/>
       <c r="B61" s="111"/>
       <c r="C61" s="111"/>
@@ -4590,7 +4579,7 @@
       <c r="T61" s="111"/>
       <c r="U61" s="111"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21">
       <c r="A62" s="111"/>
       <c r="B62" s="111"/>
       <c r="C62" s="111"/>
@@ -4613,7 +4602,7 @@
       <c r="T62" s="111"/>
       <c r="U62" s="111"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21">
       <c r="A63" s="111"/>
       <c r="B63" s="111"/>
       <c r="C63" s="111"/>
@@ -4636,7 +4625,7 @@
       <c r="T63" s="111"/>
       <c r="U63" s="111"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21">
       <c r="A64" s="111"/>
       <c r="B64" s="111"/>
       <c r="C64" s="111"/>
@@ -4659,7 +4648,7 @@
       <c r="T64" s="111"/>
       <c r="U64" s="111"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21">
       <c r="A65" s="111"/>
       <c r="B65" s="111"/>
       <c r="C65" s="111"/>
@@ -4682,7 +4671,7 @@
       <c r="T65" s="111"/>
       <c r="U65" s="111"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21">
       <c r="A66" s="111"/>
       <c r="B66" s="111"/>
       <c r="C66" s="111"/>
@@ -4705,22 +4694,22 @@
       <c r="T66" s="111"/>
       <c r="U66" s="111"/>
     </row>
-    <row r="67" spans="1:21" ht="33" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:21" ht="33">
       <c r="A67" s="111"/>
       <c r="B67" s="111"/>
       <c r="C67" s="111"/>
-      <c r="D67" s="220" t="s">
+      <c r="D67" s="215" t="s">
         <v>46</v>
       </c>
-      <c r="E67" s="221"/>
-      <c r="F67" s="221"/>
-      <c r="G67" s="221"/>
-      <c r="H67" s="221"/>
-      <c r="I67" s="221"/>
-      <c r="J67" s="221"/>
-      <c r="K67" s="221"/>
-      <c r="L67" s="221"/>
-      <c r="M67" s="222"/>
+      <c r="E67" s="216"/>
+      <c r="F67" s="216"/>
+      <c r="G67" s="216"/>
+      <c r="H67" s="216"/>
+      <c r="I67" s="216"/>
+      <c r="J67" s="216"/>
+      <c r="K67" s="216"/>
+      <c r="L67" s="216"/>
+      <c r="M67" s="217"/>
       <c r="N67" s="111"/>
       <c r="O67" s="111"/>
       <c r="P67" s="111"/>
@@ -4730,7 +4719,7 @@
       <c r="T67" s="111"/>
       <c r="U67" s="111"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21">
       <c r="A68" s="111"/>
       <c r="B68" s="111"/>
       <c r="C68" s="111"/>
@@ -4753,7 +4742,7 @@
       <c r="T68" s="111"/>
       <c r="U68" s="111"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21">
       <c r="A69" s="111"/>
       <c r="B69" s="111"/>
       <c r="C69" s="111"/>
@@ -4776,12 +4765,12 @@
       <c r="T69" s="111"/>
       <c r="U69" s="111"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" s="223" t="s">
+    <row r="70" spans="1:21">
+      <c r="A70" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="B70" s="224"/>
-      <c r="C70" s="225"/>
+      <c r="B70" s="204"/>
+      <c r="C70" s="205"/>
       <c r="D70" s="44" t="s">
         <v>26</v>
       </c>
@@ -4791,14 +4780,14 @@
       <c r="F70" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="G70" s="223" t="s">
+      <c r="G70" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="H70" s="225"/>
-      <c r="I70" s="223" t="s">
+      <c r="H70" s="205"/>
+      <c r="I70" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="J70" s="225"/>
+      <c r="J70" s="205"/>
       <c r="K70" s="111"/>
       <c r="L70" s="111"/>
       <c r="M70" s="111"/>
@@ -4811,7 +4800,7 @@
       <c r="T70" s="111"/>
       <c r="U70" s="111"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21">
       <c r="A71" s="111"/>
       <c r="B71" s="111"/>
       <c r="C71" s="111"/>
@@ -4823,20 +4812,20 @@
       <c r="I71" s="111"/>
       <c r="J71" s="111"/>
       <c r="K71" s="111"/>
-      <c r="L71" s="218" t="s">
+      <c r="L71" s="206" t="s">
         <v>44</v>
       </c>
-      <c r="M71" s="219"/>
-      <c r="N71" s="219"/>
-      <c r="O71" s="219"/>
-      <c r="P71" s="219"/>
-      <c r="Q71" s="219"/>
-      <c r="R71" s="219"/>
-      <c r="S71" s="219"/>
-      <c r="T71" s="219"/>
-      <c r="U71" s="219"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M71" s="207"/>
+      <c r="N71" s="207"/>
+      <c r="O71" s="207"/>
+      <c r="P71" s="207"/>
+      <c r="Q71" s="207"/>
+      <c r="R71" s="207"/>
+      <c r="S71" s="207"/>
+      <c r="T71" s="207"/>
+      <c r="U71" s="207"/>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" s="111"/>
       <c r="B72" s="111"/>
       <c r="C72" s="111"/>
@@ -4861,12 +4850,12 @@
       <c r="T72" s="130"/>
       <c r="U72" s="130"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="204" t="s">
+    <row r="73" spans="1:21">
+      <c r="A73" s="196" t="s">
         <v>54</v>
       </c>
-      <c r="B73" s="205"/>
-      <c r="C73" s="206"/>
+      <c r="B73" s="197"/>
+      <c r="C73" s="198"/>
       <c r="D73" s="84"/>
       <c r="E73" s="84">
         <v>51420</v>
@@ -4874,15 +4863,15 @@
       <c r="F73" s="153">
         <v>0.42799999999999999</v>
       </c>
-      <c r="G73" s="207">
+      <c r="G73" s="199">
         <f>E73*0.428</f>
         <v>22007.759999999998</v>
       </c>
-      <c r="H73" s="208"/>
-      <c r="I73" s="209">
+      <c r="H73" s="200"/>
+      <c r="I73" s="201">
         <v>22</v>
       </c>
-      <c r="J73" s="210"/>
+      <c r="J73" s="202"/>
       <c r="K73" s="111"/>
       <c r="L73" s="70">
         <v>9390</v>
@@ -4897,12 +4886,12 @@
       <c r="T73" s="70"/>
       <c r="U73" s="70"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="204" t="s">
+    <row r="74" spans="1:21">
+      <c r="A74" s="196" t="s">
         <v>55</v>
       </c>
-      <c r="B74" s="205"/>
-      <c r="C74" s="206"/>
+      <c r="B74" s="197"/>
+      <c r="C74" s="198"/>
       <c r="D74" s="84"/>
       <c r="E74" s="84">
         <v>38070</v>
@@ -4910,15 +4899,15 @@
       <c r="F74" s="153">
         <v>0.33100000000000002</v>
       </c>
-      <c r="G74" s="207">
+      <c r="G74" s="199">
         <f>E74*0.331</f>
         <v>12601.17</v>
       </c>
-      <c r="H74" s="208"/>
-      <c r="I74" s="209">
+      <c r="H74" s="200"/>
+      <c r="I74" s="201">
         <v>12</v>
       </c>
-      <c r="J74" s="210"/>
+      <c r="J74" s="202"/>
       <c r="K74" s="111"/>
       <c r="L74" s="70">
         <v>12480</v>
@@ -4933,12 +4922,12 @@
       <c r="T74" s="70"/>
       <c r="U74" s="70"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="204" t="s">
+    <row r="75" spans="1:21">
+      <c r="A75" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="B75" s="205"/>
-      <c r="C75" s="206"/>
+      <c r="B75" s="197"/>
+      <c r="C75" s="198"/>
       <c r="D75" s="84"/>
       <c r="E75" s="84">
         <v>42100</v>
@@ -4946,15 +4935,15 @@
       <c r="F75" s="153">
         <v>0.36899999999999999</v>
       </c>
-      <c r="G75" s="207">
+      <c r="G75" s="199">
         <f>E75*0.369</f>
         <v>15534.9</v>
       </c>
-      <c r="H75" s="208"/>
-      <c r="I75" s="209">
+      <c r="H75" s="200"/>
+      <c r="I75" s="201">
         <v>15</v>
       </c>
-      <c r="J75" s="210"/>
+      <c r="J75" s="202"/>
       <c r="K75" s="111"/>
       <c r="L75" s="70">
         <v>13240</v>
@@ -4969,12 +4958,12 @@
       <c r="T75" s="70"/>
       <c r="U75" s="70"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="204" t="s">
+    <row r="76" spans="1:21">
+      <c r="A76" s="196" t="s">
         <v>61</v>
       </c>
-      <c r="B76" s="205"/>
-      <c r="C76" s="206"/>
+      <c r="B76" s="197"/>
+      <c r="C76" s="198"/>
       <c r="D76" s="84"/>
       <c r="E76" s="84">
         <v>64570</v>
@@ -4982,15 +4971,15 @@
       <c r="F76" s="153">
         <v>0.48</v>
       </c>
-      <c r="G76" s="207">
+      <c r="G76" s="199">
         <f>E76*0.48</f>
         <v>30993.599999999999</v>
       </c>
-      <c r="H76" s="208"/>
-      <c r="I76" s="211">
+      <c r="H76" s="200"/>
+      <c r="I76" s="218">
         <v>31</v>
       </c>
-      <c r="J76" s="212"/>
+      <c r="J76" s="219"/>
       <c r="K76" s="111"/>
       <c r="L76" s="70"/>
       <c r="M76" s="70"/>
@@ -5003,7 +4992,7 @@
       <c r="T76" s="70"/>
       <c r="U76" s="70"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21">
       <c r="A77" s="149"/>
       <c r="B77" s="150" t="s">
         <v>66</v>
@@ -5016,15 +5005,15 @@
       <c r="F77" s="153">
         <v>0.43</v>
       </c>
-      <c r="G77" s="207">
+      <c r="G77" s="199">
         <f>E77*0.43</f>
         <v>34903.1</v>
       </c>
-      <c r="H77" s="208"/>
-      <c r="I77" s="211">
+      <c r="H77" s="200"/>
+      <c r="I77" s="218">
         <v>35</v>
       </c>
-      <c r="J77" s="212"/>
+      <c r="J77" s="219"/>
       <c r="K77" s="111"/>
       <c r="L77" s="70"/>
       <c r="M77" s="70"/>
@@ -5037,12 +5026,12 @@
       <c r="T77" s="70"/>
       <c r="U77" s="70"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="213" t="s">
+    <row r="78" spans="1:21">
+      <c r="A78" s="220" t="s">
         <v>29</v>
       </c>
-      <c r="B78" s="214"/>
-      <c r="C78" s="215"/>
+      <c r="B78" s="221"/>
+      <c r="C78" s="222"/>
       <c r="D78" s="50">
         <f>SUM(D73:D77)</f>
         <v>0</v>
@@ -5052,35 +5041,40 @@
         <v>277330</v>
       </c>
       <c r="F78" s="60"/>
-      <c r="G78" s="216">
+      <c r="G78" s="223">
         <f>SUM(G73:G77)</f>
         <v>116040.53</v>
       </c>
-      <c r="H78" s="217"/>
-      <c r="I78" s="213">
+      <c r="H78" s="224"/>
+      <c r="I78" s="220">
         <f>SUM(I73:I77)</f>
         <v>115</v>
       </c>
-      <c r="J78" s="215"/>
+      <c r="J78" s="222"/>
       <c r="L78">
         <f>SUM(L73:L77)</f>
         <v>35110</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21">
       <c r="D80" s="169"/>
     </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4">
       <c r="D81" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="I78:J78"/>
     <mergeCell ref="L71:U71"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="G73:H73"/>
@@ -5089,17 +5083,12 @@
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="D67:M67"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5112,55 +5101,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2485C30B-60FE-4803-A34A-FC87DD6C3347}">
   <sheetPr codeName="Foglio4"/>
   <dimension ref="A1:U119"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.5" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
+    <row r="1" spans="1:21" ht="26" thickBot="1">
+      <c r="A1" s="227" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
       <c r="D1" s="1">
         <v>46195</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="210" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="201"/>
-    </row>
-    <row r="2" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="209"/>
+    </row>
+    <row r="2" spans="1:21" ht="16" thickTop="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="51" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -5223,7 +5212,7 @@
       </c>
       <c r="U3" s="138"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21">
       <c r="A4" s="108" t="s">
         <v>104</v>
       </c>
@@ -5275,7 +5264,7 @@
       </c>
       <c r="U4" s="119"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="16">
       <c r="A5" s="108" t="s">
         <v>159</v>
       </c>
@@ -5329,7 +5318,7 @@
       </c>
       <c r="U5" s="119"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="16">
       <c r="A6" s="108" t="s">
         <v>159</v>
       </c>
@@ -5379,7 +5368,7 @@
       </c>
       <c r="U6" s="119"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="16">
       <c r="A7" s="81" t="s">
         <v>164</v>
       </c>
@@ -5433,7 +5422,7 @@
       </c>
       <c r="U7" s="119"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21">
       <c r="A8" s="81" t="s">
         <v>164</v>
       </c>
@@ -5485,7 +5474,7 @@
       </c>
       <c r="U8" s="119"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21">
       <c r="A9" s="81"/>
       <c r="B9" s="79"/>
       <c r="C9" s="170"/>
@@ -5511,7 +5500,7 @@
       <c r="T9" s="13"/>
       <c r="U9" s="119"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21">
       <c r="A10" s="81"/>
       <c r="B10" s="77"/>
       <c r="C10" s="170"/>
@@ -5537,7 +5526,7 @@
       <c r="T10" s="13"/>
       <c r="U10" s="119"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="A11" s="19"/>
       <c r="B11" s="74"/>
       <c r="C11" s="96"/>
@@ -5560,7 +5549,7 @@
       <c r="T11" s="13"/>
       <c r="U11" s="119"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21">
       <c r="A12" s="19"/>
       <c r="B12" s="74"/>
       <c r="C12" s="96"/>
@@ -5589,7 +5578,7 @@
       <c r="T12" s="13"/>
       <c r="U12" s="119"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="A13" s="112"/>
       <c r="B13" s="96"/>
       <c r="C13" s="99"/>
@@ -5612,7 +5601,7 @@
       <c r="T13" s="13"/>
       <c r="U13" s="119"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21">
       <c r="A14" s="112"/>
       <c r="B14" s="112"/>
       <c r="C14" s="99"/>
@@ -5635,7 +5624,7 @@
       <c r="T14" s="13"/>
       <c r="U14" s="119"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="A15" s="112"/>
       <c r="B15" s="112"/>
       <c r="C15" s="99"/>
@@ -5658,7 +5647,7 @@
       <c r="T15" s="13"/>
       <c r="U15" s="119"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="A16" s="113"/>
       <c r="B16" s="111"/>
       <c r="C16" s="70"/>
@@ -5708,7 +5697,7 @@
       <c r="T16" s="26"/>
       <c r="U16" s="119"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21">
       <c r="A17" s="108" t="s">
         <v>159</v>
       </c>
@@ -5762,7 +5751,7 @@
       </c>
       <c r="U17" s="119"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21">
       <c r="A18" s="108" t="s">
         <v>159</v>
       </c>
@@ -5816,7 +5805,7 @@
       </c>
       <c r="U18" s="119"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21">
       <c r="A19" s="108" t="s">
         <v>159</v>
       </c>
@@ -5870,7 +5859,7 @@
       </c>
       <c r="U19" s="119"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21">
       <c r="A20" s="108" t="s">
         <v>164</v>
       </c>
@@ -5924,7 +5913,7 @@
       </c>
       <c r="U20" s="119"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21">
       <c r="A21" s="108" t="s">
         <v>164</v>
       </c>
@@ -5978,7 +5967,7 @@
       </c>
       <c r="U21" s="119"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21">
       <c r="A22" s="108" t="s">
         <v>164</v>
       </c>
@@ -6032,7 +6021,7 @@
       </c>
       <c r="U22" s="119"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21">
       <c r="A23" s="108" t="s">
         <v>164</v>
       </c>
@@ -6086,7 +6075,7 @@
       </c>
       <c r="U23" s="119"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21">
       <c r="A24" s="108" t="s">
         <v>164</v>
       </c>
@@ -6136,7 +6125,7 @@
       </c>
       <c r="U24" s="119"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21">
       <c r="A25" s="108" t="s">
         <v>164</v>
       </c>
@@ -6190,7 +6179,7 @@
       </c>
       <c r="U25" s="119"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21">
       <c r="A26" s="108" t="s">
         <v>164</v>
       </c>
@@ -6242,7 +6231,7 @@
       </c>
       <c r="U26" s="119"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21">
       <c r="A27" s="108" t="s">
         <v>164</v>
       </c>
@@ -6294,7 +6283,7 @@
       </c>
       <c r="U27" s="119"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21">
       <c r="A28" s="108" t="s">
         <v>164</v>
       </c>
@@ -6346,7 +6335,7 @@
       </c>
       <c r="U28" s="119"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21">
       <c r="A29" s="108" t="s">
         <v>164</v>
       </c>
@@ -6398,7 +6387,7 @@
       </c>
       <c r="U29" s="119"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21">
       <c r="A30" s="108" t="s">
         <v>167</v>
       </c>
@@ -6450,7 +6439,7 @@
       </c>
       <c r="U30" s="119"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21">
       <c r="A31" s="108" t="s">
         <v>167</v>
       </c>
@@ -6504,7 +6493,7 @@
       </c>
       <c r="U31" s="119"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21">
       <c r="A32" s="108" t="s">
         <v>167</v>
       </c>
@@ -6558,7 +6547,7 @@
       </c>
       <c r="U32" s="119"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21">
       <c r="A33" s="108" t="s">
         <v>167</v>
       </c>
@@ -6612,7 +6601,7 @@
       </c>
       <c r="U33" s="119"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21">
       <c r="A34" s="108" t="s">
         <v>167</v>
       </c>
@@ -6654,7 +6643,7 @@
       <c r="T34" s="26"/>
       <c r="U34" s="119"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21">
       <c r="A35" s="108"/>
       <c r="B35" s="79"/>
       <c r="C35" s="79"/>
@@ -6680,7 +6669,7 @@
       <c r="T35" s="26"/>
       <c r="U35" s="119"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21">
       <c r="A36" s="114"/>
       <c r="B36" s="78"/>
       <c r="C36" s="30"/>
@@ -6705,7 +6694,7 @@
       <c r="T36" s="26"/>
       <c r="U36" s="119"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21">
       <c r="A37" s="114"/>
       <c r="B37" s="78"/>
       <c r="C37" s="30"/>
@@ -6728,7 +6717,7 @@
       <c r="T37" s="26"/>
       <c r="U37" s="119"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21">
       <c r="A38" s="114"/>
       <c r="B38" s="78"/>
       <c r="C38" s="30"/>
@@ -6757,7 +6746,7 @@
       <c r="T38" s="26"/>
       <c r="U38" s="119"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21">
       <c r="A39" s="114"/>
       <c r="B39" s="78"/>
       <c r="C39" s="30"/>
@@ -6786,7 +6775,7 @@
       <c r="T39" s="26"/>
       <c r="U39" s="119"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21">
       <c r="A40" s="114"/>
       <c r="B40" s="78"/>
       <c r="C40" s="30"/>
@@ -6815,7 +6804,7 @@
       <c r="T40" s="26"/>
       <c r="U40" s="119"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21">
       <c r="A41" s="114"/>
       <c r="B41" s="78"/>
       <c r="C41" s="30"/>
@@ -6844,7 +6833,7 @@
       <c r="T41" s="26"/>
       <c r="U41" s="119"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21">
       <c r="A42" s="114"/>
       <c r="B42" s="78"/>
       <c r="C42" s="78"/>
@@ -6867,7 +6856,7 @@
       <c r="T42" s="26"/>
       <c r="U42" s="119"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21">
       <c r="A43" s="70"/>
       <c r="B43" s="79"/>
       <c r="C43" s="79"/>
@@ -6917,7 +6906,7 @@
       <c r="T43" s="26"/>
       <c r="U43" s="119"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21">
       <c r="A44" s="108" t="s">
         <v>159</v>
       </c>
@@ -6969,7 +6958,7 @@
       </c>
       <c r="U44" s="119"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21">
       <c r="A45" s="108" t="s">
         <v>159</v>
       </c>
@@ -7021,7 +7010,7 @@
       </c>
       <c r="U45" s="119"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21">
       <c r="A46" s="108" t="s">
         <v>164</v>
       </c>
@@ -7075,7 +7064,7 @@
       </c>
       <c r="U46" s="119"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21">
       <c r="A47" s="108" t="s">
         <v>164</v>
       </c>
@@ -7127,7 +7116,7 @@
       </c>
       <c r="U47" s="119"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21">
       <c r="A48" s="108" t="s">
         <v>164</v>
       </c>
@@ -7179,7 +7168,7 @@
       </c>
       <c r="U48" s="119"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21">
       <c r="A49" s="108" t="s">
         <v>164</v>
       </c>
@@ -7233,7 +7222,7 @@
       </c>
       <c r="U49" s="119"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21">
       <c r="A50" s="108" t="s">
         <v>164</v>
       </c>
@@ -7285,7 +7274,7 @@
       </c>
       <c r="U50" s="119"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21">
       <c r="A51" s="108" t="s">
         <v>164</v>
       </c>
@@ -7335,7 +7324,7 @@
       </c>
       <c r="U51" s="119"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21">
       <c r="A52" s="108" t="s">
         <v>164</v>
       </c>
@@ -7389,7 +7378,7 @@
       </c>
       <c r="U52" s="119"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21">
       <c r="A53" s="108" t="s">
         <v>164</v>
       </c>
@@ -7441,7 +7430,7 @@
       </c>
       <c r="U53" s="119"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21">
       <c r="A54" s="108" t="s">
         <v>164</v>
       </c>
@@ -7493,7 +7482,7 @@
       </c>
       <c r="U54" s="119"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21">
       <c r="A55" s="108" t="s">
         <v>164</v>
       </c>
@@ -7545,7 +7534,7 @@
       </c>
       <c r="U55" s="119"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21">
       <c r="A56" s="108" t="s">
         <v>164</v>
       </c>
@@ -7597,7 +7586,7 @@
       </c>
       <c r="U56" s="119"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21">
       <c r="A57" s="108" t="s">
         <v>164</v>
       </c>
@@ -7649,7 +7638,7 @@
       </c>
       <c r="U57" s="119"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21">
       <c r="A58" s="108" t="s">
         <v>164</v>
       </c>
@@ -7701,7 +7690,7 @@
       </c>
       <c r="U58" s="119"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21">
       <c r="A59" s="108" t="s">
         <v>164</v>
       </c>
@@ -7753,7 +7742,7 @@
       </c>
       <c r="U59" s="119"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21">
       <c r="A60" s="108" t="s">
         <v>164</v>
       </c>
@@ -7805,7 +7794,7 @@
       </c>
       <c r="U60" s="119"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21">
       <c r="A61" s="108" t="s">
         <v>164</v>
       </c>
@@ -7859,7 +7848,7 @@
       </c>
       <c r="U61" s="119"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21">
       <c r="A62" s="108" t="s">
         <v>167</v>
       </c>
@@ -7913,7 +7902,7 @@
       </c>
       <c r="U62" s="119"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21">
       <c r="A63" s="108" t="s">
         <v>167</v>
       </c>
@@ -7967,7 +7956,7 @@
       </c>
       <c r="U63" s="119"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21">
       <c r="A64" s="108" t="s">
         <v>167</v>
       </c>
@@ -8021,7 +8010,7 @@
       </c>
       <c r="U64" s="119"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21">
       <c r="A65" s="108" t="s">
         <v>167</v>
       </c>
@@ -8075,7 +8064,7 @@
       </c>
       <c r="U65" s="119"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21">
       <c r="A66" s="108" t="s">
         <v>167</v>
       </c>
@@ -8129,7 +8118,7 @@
       </c>
       <c r="U66" s="119"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21">
       <c r="A67" s="108" t="s">
         <v>167</v>
       </c>
@@ -8183,7 +8172,7 @@
       </c>
       <c r="U67" s="119"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21">
       <c r="A68" s="108" t="s">
         <v>167</v>
       </c>
@@ -8237,7 +8226,7 @@
       </c>
       <c r="U68" s="119"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21">
       <c r="A69" s="108"/>
       <c r="B69" s="79"/>
       <c r="C69" s="79"/>
@@ -8263,7 +8252,7 @@
       <c r="T69" s="26"/>
       <c r="U69" s="119"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21">
       <c r="A70" s="34"/>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
@@ -8288,7 +8277,7 @@
       <c r="T70" s="26"/>
       <c r="U70" s="119"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21">
       <c r="A71" s="34"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
@@ -8311,7 +8300,7 @@
       <c r="T71" s="26"/>
       <c r="U71" s="119"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21">
       <c r="A72" s="34"/>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
@@ -8340,7 +8329,7 @@
       <c r="T72" s="26"/>
       <c r="U72" s="119"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21">
       <c r="A73" s="34"/>
       <c r="B73" s="35"/>
       <c r="C73" s="80"/>
@@ -8369,7 +8358,7 @@
       <c r="T73" s="26"/>
       <c r="U73" s="119"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21">
       <c r="A74" s="34"/>
       <c r="B74" s="35"/>
       <c r="C74" s="80"/>
@@ -8398,7 +8387,7 @@
       <c r="T74" s="26"/>
       <c r="U74" s="119"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21">
       <c r="A75" s="34"/>
       <c r="B75" s="35"/>
       <c r="C75" s="80"/>
@@ -8421,7 +8410,7 @@
       <c r="T75" s="26"/>
       <c r="U75" s="119"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21">
       <c r="A76" s="70"/>
       <c r="B76" s="131"/>
       <c r="C76" s="70"/>
@@ -8471,7 +8460,7 @@
       <c r="T76" s="26"/>
       <c r="U76" s="119"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21">
       <c r="A77" s="108"/>
       <c r="B77" s="79"/>
       <c r="C77" s="79"/>
@@ -8497,7 +8486,7 @@
       <c r="T77" s="94"/>
       <c r="U77" s="123"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21">
       <c r="A78" s="108"/>
       <c r="B78" s="79"/>
       <c r="C78" s="79"/>
@@ -8523,7 +8512,7 @@
       <c r="T78" s="94"/>
       <c r="U78" s="123"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21">
       <c r="A79" s="108" t="s">
         <v>159</v>
       </c>
@@ -8575,7 +8564,7 @@
       </c>
       <c r="U79" s="123"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21">
       <c r="A80" s="108" t="s">
         <v>159</v>
       </c>
@@ -8627,7 +8616,7 @@
       </c>
       <c r="U80" s="123"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21">
       <c r="A81" s="108" t="s">
         <v>164</v>
       </c>
@@ -8679,7 +8668,7 @@
       </c>
       <c r="U81" s="123"/>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21">
       <c r="A82" s="108" t="s">
         <v>164</v>
       </c>
@@ -8731,7 +8720,7 @@
       </c>
       <c r="U82" s="123"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21">
       <c r="A83" s="108" t="s">
         <v>164</v>
       </c>
@@ -8783,7 +8772,7 @@
       </c>
       <c r="U83" s="123"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21">
       <c r="A84" s="108" t="s">
         <v>164</v>
       </c>
@@ -8835,7 +8824,7 @@
       </c>
       <c r="U84" s="123"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21">
       <c r="A85" s="108" t="s">
         <v>167</v>
       </c>
@@ -8887,7 +8876,7 @@
       </c>
       <c r="U85" s="123"/>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21">
       <c r="A86" s="108" t="s">
         <v>167</v>
       </c>
@@ -8939,7 +8928,7 @@
       </c>
       <c r="U86" s="123"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21">
       <c r="A87" s="108" t="s">
         <v>167</v>
       </c>
@@ -8991,7 +8980,7 @@
       </c>
       <c r="U87" s="123"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21">
       <c r="A88" s="81"/>
       <c r="B88" s="132"/>
       <c r="C88" s="82"/>
@@ -9017,7 +9006,7 @@
       <c r="T88" s="29"/>
       <c r="U88" s="123"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21">
       <c r="A89" s="124"/>
       <c r="B89" s="133"/>
       <c r="C89" s="125"/>
@@ -9040,7 +9029,7 @@
       <c r="T89" s="18"/>
       <c r="U89" s="122"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21">
       <c r="A90" s="124"/>
       <c r="B90" s="133"/>
       <c r="C90" s="125"/>
@@ -9063,7 +9052,7 @@
       <c r="T90" s="18"/>
       <c r="U90" s="122"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21">
       <c r="A91" s="127"/>
       <c r="B91" s="134"/>
       <c r="C91" s="125"/>
@@ -9086,7 +9075,7 @@
       <c r="T91" s="18"/>
       <c r="U91" s="123"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21">
       <c r="A92" s="128"/>
       <c r="B92" s="135"/>
       <c r="C92" s="129"/>
@@ -9136,7 +9125,7 @@
       <c r="T92" s="18"/>
       <c r="U92" s="123"/>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21">
       <c r="A93" s="128"/>
       <c r="B93" s="135"/>
       <c r="C93" s="129"/>
@@ -9159,7 +9148,7 @@
       <c r="T93" s="18"/>
       <c r="U93" s="123"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21">
       <c r="A94" s="81" t="s">
         <v>164</v>
       </c>
@@ -9181,7 +9170,9 @@
       <c r="G94" s="47"/>
       <c r="H94" s="47"/>
       <c r="I94" s="47"/>
-      <c r="J94" s="70"/>
+      <c r="J94" s="70">
+        <v>665</v>
+      </c>
       <c r="K94" s="68" t="s">
         <v>78</v>
       </c>
@@ -9208,7 +9199,7 @@
       </c>
       <c r="U94" s="123"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21">
       <c r="A95" s="81" t="s">
         <v>164</v>
       </c>
@@ -9230,7 +9221,9 @@
       <c r="G95" s="46"/>
       <c r="H95" s="47"/>
       <c r="I95" s="46"/>
-      <c r="J95" s="70"/>
+      <c r="J95" s="70">
+        <v>653</v>
+      </c>
       <c r="K95" s="68" t="s">
         <v>78</v>
       </c>
@@ -9257,7 +9250,7 @@
       </c>
       <c r="U95" s="123"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21">
       <c r="A96" s="70"/>
       <c r="B96" s="131"/>
       <c r="C96" s="70"/>
@@ -9307,7 +9300,7 @@
       <c r="T96" s="26"/>
       <c r="U96" s="111"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21">
       <c r="A97" s="70"/>
       <c r="B97" s="131"/>
       <c r="C97" s="81"/>
@@ -9330,7 +9323,7 @@
       <c r="T97" s="26"/>
       <c r="U97" s="111"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21">
       <c r="A98" s="70"/>
       <c r="B98" s="131"/>
       <c r="C98" s="70"/>
@@ -9353,14 +9346,14 @@
       <c r="T98" s="70"/>
       <c r="U98" s="111"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21">
       <c r="A99" s="70"/>
       <c r="B99" s="131"/>
       <c r="C99" s="70"/>
-      <c r="D99" s="202" t="s">
+      <c r="D99" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="E99" s="203"/>
+      <c r="E99" s="214"/>
       <c r="F99" s="39">
         <f>SUM(F16,F43,F76,F92,F96)</f>
         <v>54296</v>
@@ -9401,7 +9394,7 @@
       <c r="T99" s="70"/>
       <c r="U99" s="111"/>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21">
       <c r="A100" s="111"/>
       <c r="B100" s="111"/>
       <c r="C100" s="111"/>
@@ -9424,7 +9417,7 @@
       <c r="T100" s="111"/>
       <c r="U100" s="111"/>
     </row>
-    <row r="101" spans="1:21" ht="18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" ht="18">
       <c r="A101" s="111"/>
       <c r="B101" s="111"/>
       <c r="C101" s="111"/>
@@ -9452,7 +9445,7 @@
       <c r="T101" s="111"/>
       <c r="U101" s="111"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21">
       <c r="A102" s="111"/>
       <c r="B102" s="111"/>
       <c r="C102" s="111"/>
@@ -9475,7 +9468,7 @@
       <c r="T102" s="111"/>
       <c r="U102" s="111"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21">
       <c r="A103" s="111"/>
       <c r="B103" s="111"/>
       <c r="C103" s="111"/>
@@ -9498,7 +9491,7 @@
       <c r="T103" s="111"/>
       <c r="U103" s="111"/>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21">
       <c r="A104" s="111"/>
       <c r="B104" s="111"/>
       <c r="C104" s="111"/>
@@ -9521,7 +9514,7 @@
       <c r="T104" s="111"/>
       <c r="U104" s="111"/>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21">
       <c r="A105" s="111"/>
       <c r="B105" s="111"/>
       <c r="C105" s="111"/>
@@ -9544,7 +9537,7 @@
       <c r="T105" s="111"/>
       <c r="U105" s="111"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21">
       <c r="A106" s="111"/>
       <c r="B106" s="111"/>
       <c r="C106" s="111"/>
@@ -9567,7 +9560,7 @@
       <c r="T106" s="111"/>
       <c r="U106" s="111"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21">
       <c r="A107" s="111"/>
       <c r="B107" s="111"/>
       <c r="C107" s="111"/>
@@ -9590,22 +9583,22 @@
       <c r="T107" s="111"/>
       <c r="U107" s="111"/>
     </row>
-    <row r="108" spans="1:21" ht="33" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:21" ht="33">
       <c r="A108" s="111"/>
       <c r="B108" s="111"/>
       <c r="C108" s="111"/>
-      <c r="D108" s="220" t="s">
+      <c r="D108" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="E108" s="221"/>
-      <c r="F108" s="221"/>
-      <c r="G108" s="221"/>
-      <c r="H108" s="221"/>
-      <c r="I108" s="221"/>
-      <c r="J108" s="221"/>
-      <c r="K108" s="221"/>
-      <c r="L108" s="221"/>
-      <c r="M108" s="222"/>
+      <c r="E108" s="216"/>
+      <c r="F108" s="216"/>
+      <c r="G108" s="216"/>
+      <c r="H108" s="216"/>
+      <c r="I108" s="216"/>
+      <c r="J108" s="216"/>
+      <c r="K108" s="216"/>
+      <c r="L108" s="216"/>
+      <c r="M108" s="217"/>
       <c r="N108" s="111"/>
       <c r="O108" s="111"/>
       <c r="P108" s="111"/>
@@ -9615,7 +9608,7 @@
       <c r="T108" s="111"/>
       <c r="U108" s="111"/>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21">
       <c r="A109" s="111"/>
       <c r="B109" s="111"/>
       <c r="C109" s="111"/>
@@ -9638,7 +9631,7 @@
       <c r="T109" s="111"/>
       <c r="U109" s="111"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21">
       <c r="A110" s="111"/>
       <c r="B110" s="111"/>
       <c r="C110" s="111"/>
@@ -9661,12 +9654,12 @@
       <c r="T110" s="111"/>
       <c r="U110" s="111"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" s="223" t="s">
+    <row r="111" spans="1:21">
+      <c r="A111" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="B111" s="224"/>
-      <c r="C111" s="225"/>
+      <c r="B111" s="204"/>
+      <c r="C111" s="205"/>
       <c r="D111" s="44" t="s">
         <v>26</v>
       </c>
@@ -9676,14 +9669,14 @@
       <c r="F111" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="G111" s="223" t="s">
+      <c r="G111" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="H111" s="225"/>
-      <c r="I111" s="223" t="s">
+      <c r="H111" s="205"/>
+      <c r="I111" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="J111" s="225"/>
+      <c r="J111" s="205"/>
       <c r="K111" s="111"/>
       <c r="L111" s="111"/>
       <c r="M111" s="111"/>
@@ -9696,7 +9689,7 @@
       <c r="T111" s="111"/>
       <c r="U111" s="111"/>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21">
       <c r="A112" s="111"/>
       <c r="B112" s="111"/>
       <c r="C112" s="111"/>
@@ -9708,20 +9701,20 @@
       <c r="I112" s="111"/>
       <c r="J112" s="111"/>
       <c r="K112" s="111"/>
-      <c r="L112" s="218" t="s">
+      <c r="L112" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="M112" s="219"/>
-      <c r="N112" s="219"/>
-      <c r="O112" s="219"/>
-      <c r="P112" s="219"/>
-      <c r="Q112" s="219"/>
-      <c r="R112" s="219"/>
-      <c r="S112" s="219"/>
-      <c r="T112" s="219"/>
-      <c r="U112" s="219"/>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M112" s="207"/>
+      <c r="N112" s="207"/>
+      <c r="O112" s="207"/>
+      <c r="P112" s="207"/>
+      <c r="Q112" s="207"/>
+      <c r="R112" s="207"/>
+      <c r="S112" s="207"/>
+      <c r="T112" s="207"/>
+      <c r="U112" s="207"/>
+    </row>
+    <row r="113" spans="1:21">
       <c r="A113" s="111"/>
       <c r="B113" s="111"/>
       <c r="C113" s="111"/>
@@ -9744,12 +9737,12 @@
       <c r="T113" s="130"/>
       <c r="U113" s="130"/>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" s="204" t="s">
+    <row r="114" spans="1:21">
+      <c r="A114" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="B114" s="205"/>
-      <c r="C114" s="206"/>
+      <c r="B114" s="197"/>
+      <c r="C114" s="198"/>
       <c r="D114" s="49"/>
       <c r="E114" s="84">
         <v>80240</v>
@@ -9757,15 +9750,15 @@
       <c r="F114" s="153">
         <v>0.40699999999999997</v>
       </c>
-      <c r="G114" s="207">
+      <c r="G114" s="199">
         <f>E114*0.407</f>
         <v>32657.679999999997</v>
       </c>
-      <c r="H114" s="208"/>
-      <c r="I114" s="209">
+      <c r="H114" s="200"/>
+      <c r="I114" s="201">
         <v>32</v>
       </c>
-      <c r="J114" s="210"/>
+      <c r="J114" s="202"/>
       <c r="K114" s="111"/>
       <c r="L114" s="70"/>
       <c r="M114" s="70"/>
@@ -9778,12 +9771,12 @@
       <c r="T114" s="70"/>
       <c r="U114" s="70"/>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="204" t="s">
+    <row r="115" spans="1:21">
+      <c r="A115" s="196" t="s">
         <v>51</v>
       </c>
-      <c r="B115" s="205"/>
-      <c r="C115" s="206"/>
+      <c r="B115" s="197"/>
+      <c r="C115" s="198"/>
       <c r="D115" s="49"/>
       <c r="E115" s="84">
         <v>90710</v>
@@ -9791,15 +9784,15 @@
       <c r="F115" s="153">
         <v>0.376</v>
       </c>
-      <c r="G115" s="207">
+      <c r="G115" s="199">
         <f>E115*0.376</f>
         <v>34106.959999999999</v>
       </c>
-      <c r="H115" s="208"/>
-      <c r="I115" s="209">
+      <c r="H115" s="200"/>
+      <c r="I115" s="201">
         <v>34</v>
       </c>
-      <c r="J115" s="210"/>
+      <c r="J115" s="202"/>
       <c r="K115" s="111"/>
       <c r="L115" s="70"/>
       <c r="M115" s="70"/>
@@ -9812,12 +9805,12 @@
       <c r="T115" s="70"/>
       <c r="U115" s="70"/>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A116" s="204" t="s">
+    <row r="116" spans="1:21">
+      <c r="A116" s="196" t="s">
         <v>52</v>
       </c>
-      <c r="B116" s="205"/>
-      <c r="C116" s="206"/>
+      <c r="B116" s="197"/>
+      <c r="C116" s="198"/>
       <c r="D116" s="49"/>
       <c r="E116" s="84">
         <v>81600</v>
@@ -9825,15 +9818,15 @@
       <c r="F116" s="153">
         <v>0.40799999999999997</v>
       </c>
-      <c r="G116" s="207">
+      <c r="G116" s="199">
         <f>E116*0.408</f>
         <v>33292.799999999996</v>
       </c>
-      <c r="H116" s="208"/>
-      <c r="I116" s="209">
+      <c r="H116" s="200"/>
+      <c r="I116" s="201">
         <v>33</v>
       </c>
-      <c r="J116" s="210"/>
+      <c r="J116" s="202"/>
       <c r="K116" s="111"/>
       <c r="L116" s="70"/>
       <c r="M116" s="70"/>
@@ -9846,12 +9839,12 @@
       <c r="T116" s="70"/>
       <c r="U116" s="70"/>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A117" s="204" t="s">
+    <row r="117" spans="1:21">
+      <c r="A117" s="196" t="s">
         <v>53</v>
       </c>
-      <c r="B117" s="205"/>
-      <c r="C117" s="206"/>
+      <c r="B117" s="197"/>
+      <c r="C117" s="198"/>
       <c r="D117" s="49"/>
       <c r="E117" s="148">
         <v>89.73</v>
@@ -9859,15 +9852,15 @@
       <c r="F117" s="71">
         <v>0.35</v>
       </c>
-      <c r="G117" s="226">
+      <c r="G117" s="225">
         <f>E117*0.35</f>
         <v>31.4055</v>
       </c>
-      <c r="H117" s="227"/>
-      <c r="I117" s="211">
+      <c r="H117" s="226"/>
+      <c r="I117" s="218">
         <v>31</v>
       </c>
-      <c r="J117" s="212"/>
+      <c r="J117" s="219"/>
       <c r="K117" s="111"/>
       <c r="L117" s="70"/>
       <c r="M117" s="70"/>
@@ -9880,7 +9873,7 @@
       <c r="T117" s="70"/>
       <c r="U117" s="70"/>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21">
       <c r="A118" s="149"/>
       <c r="B118" s="150" t="s">
         <v>77</v>
@@ -9893,15 +9886,15 @@
       <c r="F118" s="71">
         <v>0.45400000000000001</v>
       </c>
-      <c r="G118" s="207">
+      <c r="G118" s="199">
         <f>E118*0.454</f>
         <v>15708.4</v>
       </c>
-      <c r="H118" s="208"/>
-      <c r="I118" s="211">
+      <c r="H118" s="200"/>
+      <c r="I118" s="218">
         <v>15</v>
       </c>
-      <c r="J118" s="212"/>
+      <c r="J118" s="219"/>
       <c r="K118" s="111"/>
       <c r="L118" s="70"/>
       <c r="M118" s="70"/>
@@ -9914,12 +9907,12 @@
       <c r="T118" s="70"/>
       <c r="U118" s="70"/>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="213" t="s">
+    <row r="119" spans="1:21">
+      <c r="A119" s="220" t="s">
         <v>29</v>
       </c>
-      <c r="B119" s="214"/>
-      <c r="C119" s="215"/>
+      <c r="B119" s="221"/>
+      <c r="C119" s="222"/>
       <c r="D119" s="50">
         <f>SUM(D114:D118)</f>
         <v>0</v>
@@ -9929,19 +9922,28 @@
         <v>287239.73</v>
       </c>
       <c r="F119" s="60"/>
-      <c r="G119" s="216">
+      <c r="G119" s="223">
         <f>SUM(G114:G118)</f>
         <v>115797.24549999999</v>
       </c>
-      <c r="H119" s="217"/>
-      <c r="I119" s="213">
+      <c r="H119" s="224"/>
+      <c r="I119" s="220">
         <f>SUM(I114:I118)</f>
         <v>145</v>
       </c>
-      <c r="J119" s="215"/>
+      <c r="J119" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="D108:M108"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="I111:J111"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="G119:H119"/>
     <mergeCell ref="I119:J119"/>
@@ -9958,15 +9960,6 @@
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="G114:H114"/>
     <mergeCell ref="I114:J114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="D108:M108"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="I111:J111"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9978,48 +9971,48 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D0BCFC-8D99-4CB2-8136-DC59AB3A3D2A}">
   <dimension ref="A1:T356"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" customWidth="1"/>
-    <col min="13" max="15" width="10.28515625" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.140625" customWidth="1"/>
-    <col min="18" max="19" width="9.28515625" customWidth="1"/>
+    <col min="1" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="37.1640625" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="21.5" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" customWidth="1"/>
+    <col min="17" max="17" width="7.1640625" customWidth="1"/>
+    <col min="18" max="19" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
+    <row r="1" spans="1:20" ht="26" thickBot="1">
+      <c r="A1" s="227" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
       <c r="D1" s="1">
         <v>46195</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="200" t="s">
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="208" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="201"/>
-    </row>
-    <row r="2" spans="1:20" ht="39" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="209"/>
+    </row>
+    <row r="2" spans="1:20" ht="33" thickTop="1">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -10081,7 +10074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" s="81" t="s">
         <v>116</v>
       </c>
@@ -10132,7 +10125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" s="81" t="s">
         <v>183</v>
       </c>
@@ -10183,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" s="81" t="s">
         <v>183</v>
       </c>
@@ -10234,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" s="81" t="s">
         <v>194</v>
       </c>
@@ -10281,7 +10274,7 @@
       <c r="S6" s="16"/>
       <c r="T6" s="13"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" s="81" t="s">
         <v>241</v>
       </c>
@@ -10328,7 +10321,7 @@
       <c r="S7" s="16"/>
       <c r="T7" s="13"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" s="81" t="s">
         <v>241</v>
       </c>
@@ -10375,7 +10368,7 @@
       <c r="S8" s="16"/>
       <c r="T8" s="13"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" s="81" t="s">
         <v>241</v>
       </c>
@@ -10422,7 +10415,7 @@
       <c r="S9" s="16"/>
       <c r="T9" s="13"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" s="81" t="s">
         <v>241</v>
       </c>
@@ -10469,7 +10462,7 @@
       <c r="S10" s="16"/>
       <c r="T10" s="13"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" s="81" t="s">
         <v>241</v>
       </c>
@@ -10516,7 +10509,7 @@
       <c r="S11" s="16"/>
       <c r="T11" s="13"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" s="81"/>
       <c r="B12" s="118"/>
       <c r="C12" s="45"/>
@@ -10541,7 +10534,7 @@
       <c r="S12" s="16"/>
       <c r="T12" s="13"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" s="81"/>
       <c r="B13" s="118"/>
       <c r="C13" s="45"/>
@@ -10566,7 +10559,7 @@
       <c r="S13" s="16"/>
       <c r="T13" s="13"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" s="81"/>
       <c r="B14" s="118"/>
       <c r="C14" s="45"/>
@@ -10591,7 +10584,7 @@
       <c r="S14" s="16"/>
       <c r="T14" s="13"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" s="81"/>
       <c r="B15" s="118"/>
       <c r="C15" s="45"/>
@@ -10616,7 +10609,7 @@
       <c r="S15" s="16"/>
       <c r="T15" s="13"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" s="81"/>
       <c r="B16" s="118"/>
       <c r="C16" s="45"/>
@@ -10641,7 +10634,7 @@
       <c r="S16" s="16"/>
       <c r="T16" s="13"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20">
       <c r="A17" s="81" t="s">
         <v>194</v>
       </c>
@@ -10688,7 +10681,7 @@
       </c>
       <c r="T17" s="13"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20">
       <c r="A18" s="81" t="s">
         <v>194</v>
       </c>
@@ -10735,7 +10728,7 @@
       </c>
       <c r="T18" s="13"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20">
       <c r="A19" s="81" t="s">
         <v>232</v>
       </c>
@@ -10774,7 +10767,7 @@
       <c r="S19" s="16"/>
       <c r="T19" s="13"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20">
       <c r="A20" s="81"/>
       <c r="B20" s="118"/>
       <c r="C20" s="45"/>
@@ -10799,7 +10792,7 @@
       <c r="S20" s="16"/>
       <c r="T20" s="13"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20">
       <c r="A21" s="81" t="s">
         <v>213</v>
       </c>
@@ -10846,7 +10839,7 @@
       <c r="S21" s="16"/>
       <c r="T21" s="13"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20">
       <c r="A22" s="81" t="s">
         <v>216</v>
       </c>
@@ -10893,7 +10886,7 @@
       <c r="S22" s="16"/>
       <c r="T22" s="13"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20">
       <c r="A23" s="81" t="s">
         <v>216</v>
       </c>
@@ -10940,7 +10933,7 @@
       <c r="S23" s="16"/>
       <c r="T23" s="13"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20">
       <c r="A24" s="81"/>
       <c r="B24" s="118"/>
       <c r="C24" s="45"/>
@@ -10965,7 +10958,7 @@
       <c r="S24" s="16"/>
       <c r="T24" s="13"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20">
       <c r="A25" s="19"/>
       <c r="B25" s="74"/>
       <c r="C25" s="96"/>
@@ -10989,7 +10982,7 @@
       <c r="S25" s="17"/>
       <c r="T25" s="13"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20">
       <c r="A26" s="19"/>
       <c r="B26" s="74"/>
       <c r="C26" s="96"/>
@@ -11011,7 +11004,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="13"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20">
       <c r="A27" s="112"/>
       <c r="B27" s="96"/>
       <c r="C27" s="99"/>
@@ -11033,7 +11026,7 @@
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20">
       <c r="A28" s="113"/>
       <c r="B28" s="111"/>
       <c r="C28" s="70"/>
@@ -11082,7 +11075,7 @@
       <c r="S28" s="26"/>
       <c r="T28" s="26"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20">
       <c r="A29" s="81"/>
       <c r="B29" s="118"/>
       <c r="C29" s="45"/>
@@ -11104,7 +11097,7 @@
       <c r="S29" s="18"/>
       <c r="T29" s="26"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="A30" s="81" t="s">
         <v>79</v>
       </c>
@@ -11153,7 +11146,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20">
       <c r="A31" s="81"/>
       <c r="B31" s="118"/>
       <c r="C31" s="45"/>
@@ -11175,7 +11168,7 @@
       <c r="S31" s="18"/>
       <c r="T31" s="26"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20">
       <c r="A32" s="81" t="s">
         <v>104</v>
       </c>
@@ -11222,7 +11215,7 @@
       </c>
       <c r="T32" s="26"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20">
       <c r="A33" s="81" t="s">
         <v>104</v>
       </c>
@@ -11269,7 +11262,7 @@
       </c>
       <c r="T33" s="26"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20">
       <c r="A34" s="81" t="s">
         <v>121</v>
       </c>
@@ -11316,7 +11309,7 @@
       </c>
       <c r="T34" s="26"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20">
       <c r="A35" s="81" t="s">
         <v>121</v>
       </c>
@@ -11363,7 +11356,7 @@
       </c>
       <c r="T35" s="26"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20">
       <c r="A36" s="81" t="s">
         <v>121</v>
       </c>
@@ -11410,7 +11403,7 @@
       </c>
       <c r="T36" s="26"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20">
       <c r="A37" s="81" t="s">
         <v>138</v>
       </c>
@@ -11457,7 +11450,7 @@
       </c>
       <c r="T37" s="26"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20">
       <c r="A38" s="81" t="s">
         <v>138</v>
       </c>
@@ -11504,7 +11497,7 @@
       </c>
       <c r="T38" s="26"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20">
       <c r="A39" s="81" t="s">
         <v>138</v>
       </c>
@@ -11551,7 +11544,7 @@
       </c>
       <c r="T39" s="26"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20">
       <c r="A40" s="81" t="s">
         <v>138</v>
       </c>
@@ -11598,7 +11591,7 @@
       </c>
       <c r="T40" s="26"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20">
       <c r="A41" s="81" t="s">
         <v>138</v>
       </c>
@@ -11645,7 +11638,7 @@
       </c>
       <c r="T41" s="26"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20">
       <c r="A42" s="81" t="s">
         <v>138</v>
       </c>
@@ -11692,7 +11685,7 @@
       </c>
       <c r="T42" s="26"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20">
       <c r="A43" s="81" t="s">
         <v>153</v>
       </c>
@@ -11739,7 +11732,7 @@
       </c>
       <c r="T43" s="26"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20">
       <c r="A44" s="81" t="s">
         <v>153</v>
       </c>
@@ -11786,7 +11779,7 @@
       </c>
       <c r="T44" s="26"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20">
       <c r="A45" s="81" t="s">
         <v>153</v>
       </c>
@@ -11833,7 +11826,7 @@
       </c>
       <c r="T45" s="26"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20">
       <c r="A46" s="81" t="s">
         <v>153</v>
       </c>
@@ -11880,7 +11873,7 @@
       </c>
       <c r="T46" s="26"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20">
       <c r="A47" s="81"/>
       <c r="B47" s="118"/>
       <c r="C47" s="45"/>
@@ -11902,7 +11895,7 @@
       <c r="S47" s="18"/>
       <c r="T47" s="26"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20">
       <c r="A48" s="81" t="s">
         <v>194</v>
       </c>
@@ -11949,7 +11942,7 @@
       </c>
       <c r="T48" s="26"/>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20">
       <c r="A49" s="81" t="s">
         <v>194</v>
       </c>
@@ -11996,7 +11989,7 @@
       </c>
       <c r="T49" s="26"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20">
       <c r="A50" s="81" t="s">
         <v>194</v>
       </c>
@@ -12043,7 +12036,7 @@
       </c>
       <c r="T50" s="26"/>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20">
       <c r="A51" s="81" t="s">
         <v>194</v>
       </c>
@@ -12090,7 +12083,7 @@
       </c>
       <c r="T51" s="26"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20">
       <c r="A52" s="81" t="s">
         <v>194</v>
       </c>
@@ -12137,7 +12130,7 @@
       </c>
       <c r="T52" s="26"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20">
       <c r="A53" s="81" t="s">
         <v>196</v>
       </c>
@@ -12184,7 +12177,7 @@
       </c>
       <c r="T53" s="26"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20">
       <c r="A54" s="81" t="s">
         <v>196</v>
       </c>
@@ -12231,7 +12224,7 @@
       </c>
       <c r="T54" s="26"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20">
       <c r="A55" s="81" t="s">
         <v>216</v>
       </c>
@@ -12278,7 +12271,7 @@
       </c>
       <c r="T55" s="26"/>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20">
       <c r="A56" s="81" t="s">
         <v>216</v>
       </c>
@@ -12325,7 +12318,7 @@
       </c>
       <c r="T56" s="26"/>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20">
       <c r="A57" s="81" t="s">
         <v>216</v>
       </c>
@@ -12372,7 +12365,7 @@
       </c>
       <c r="T57" s="26"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20">
       <c r="A58" s="81" t="s">
         <v>244</v>
       </c>
@@ -12419,7 +12412,7 @@
       </c>
       <c r="T58" s="26"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20">
       <c r="A59" s="81" t="s">
         <v>244</v>
       </c>
@@ -12466,7 +12459,7 @@
       </c>
       <c r="T59" s="26"/>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20">
       <c r="A60" s="81" t="s">
         <v>244</v>
       </c>
@@ -12513,7 +12506,7 @@
       </c>
       <c r="T60" s="26"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20">
       <c r="A61" s="81" t="s">
         <v>244</v>
       </c>
@@ -12560,7 +12553,7 @@
       </c>
       <c r="T61" s="26"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20">
       <c r="A62" s="81" t="s">
         <v>244</v>
       </c>
@@ -12607,7 +12600,7 @@
       </c>
       <c r="T62" s="26"/>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20">
       <c r="A63" s="81" t="s">
         <v>244</v>
       </c>
@@ -12654,7 +12647,7 @@
       </c>
       <c r="T63" s="26"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20">
       <c r="A64" s="81"/>
       <c r="B64" s="118"/>
       <c r="C64" s="45"/>
@@ -12676,7 +12669,7 @@
       <c r="S64" s="18"/>
       <c r="T64" s="26"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20">
       <c r="A65" s="81"/>
       <c r="B65" s="118"/>
       <c r="C65" s="45"/>
@@ -12698,7 +12691,7 @@
       <c r="S65" s="18"/>
       <c r="T65" s="26"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20">
       <c r="A66" s="81"/>
       <c r="B66" s="118"/>
       <c r="C66" s="45"/>
@@ -12720,7 +12713,7 @@
       <c r="S66" s="18"/>
       <c r="T66" s="26"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20">
       <c r="A67" s="81"/>
       <c r="B67" s="118"/>
       <c r="C67" s="45"/>
@@ -12742,7 +12735,7 @@
       <c r="S67" s="18"/>
       <c r="T67" s="26"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20">
       <c r="A68" s="81"/>
       <c r="B68" s="118"/>
       <c r="C68" s="45"/>
@@ -12764,7 +12757,7 @@
       <c r="S68" s="18"/>
       <c r="T68" s="26"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20">
       <c r="A69" s="81"/>
       <c r="B69" s="118"/>
       <c r="C69" s="45"/>
@@ -12786,7 +12779,7 @@
       <c r="S69" s="18"/>
       <c r="T69" s="26"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20">
       <c r="A70" s="81"/>
       <c r="B70" s="118"/>
       <c r="C70" s="45"/>
@@ -12811,7 +12804,7 @@
       <c r="S70" s="18"/>
       <c r="T70" s="26"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20">
       <c r="A71" s="81" t="s">
         <v>106</v>
       </c>
@@ -12862,7 +12855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20">
       <c r="A72" s="81" t="s">
         <v>106</v>
       </c>
@@ -12913,7 +12906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20">
       <c r="A73" s="81" t="s">
         <v>106</v>
       </c>
@@ -12964,7 +12957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20">
       <c r="A74" s="81" t="s">
         <v>106</v>
       </c>
@@ -13015,7 +13008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20">
       <c r="A75" s="81" t="s">
         <v>106</v>
       </c>
@@ -13066,7 +13059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="31">
       <c r="A76" s="81" t="s">
         <v>106</v>
       </c>
@@ -13119,7 +13112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20">
       <c r="A77" s="81" t="s">
         <v>106</v>
       </c>
@@ -13170,7 +13163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20">
       <c r="A78" s="81" t="s">
         <v>106</v>
       </c>
@@ -13221,7 +13214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20">
       <c r="A79" s="81" t="s">
         <v>106</v>
       </c>
@@ -13272,7 +13265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20">
       <c r="A80" s="81" t="s">
         <v>106</v>
       </c>
@@ -13323,7 +13316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20">
       <c r="A81" s="81" t="s">
         <v>106</v>
       </c>
@@ -13374,7 +13367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20">
       <c r="A82" s="81" t="s">
         <v>106</v>
       </c>
@@ -13425,7 +13418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20">
       <c r="A83" s="81" t="s">
         <v>106</v>
       </c>
@@ -13476,7 +13469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20">
       <c r="A84" s="81" t="s">
         <v>106</v>
       </c>
@@ -13527,7 +13520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20">
       <c r="A85" s="81" t="s">
         <v>106</v>
       </c>
@@ -13578,7 +13571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20">
       <c r="A86" s="81" t="s">
         <v>106</v>
       </c>
@@ -13629,7 +13622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20">
       <c r="A87" s="81" t="s">
         <v>106</v>
       </c>
@@ -13680,7 +13673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20">
       <c r="A88" s="81" t="s">
         <v>106</v>
       </c>
@@ -13731,7 +13724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20">
       <c r="A89" s="81" t="s">
         <v>106</v>
       </c>
@@ -13782,7 +13775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20">
       <c r="A90" s="81" t="s">
         <v>116</v>
       </c>
@@ -13833,7 +13826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20">
       <c r="A91" s="81" t="s">
         <v>116</v>
       </c>
@@ -13884,7 +13877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20">
       <c r="A92" s="81" t="s">
         <v>183</v>
       </c>
@@ -13935,7 +13928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20">
       <c r="A93" s="81" t="s">
         <v>183</v>
       </c>
@@ -13986,7 +13979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20">
       <c r="A94" s="81" t="s">
         <v>183</v>
       </c>
@@ -14037,7 +14030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20">
       <c r="A95" s="81" t="s">
         <v>183</v>
       </c>
@@ -14088,7 +14081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20">
       <c r="A96" s="81" t="s">
         <v>183</v>
       </c>
@@ -14139,7 +14132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20">
       <c r="A97" s="81" t="s">
         <v>183</v>
       </c>
@@ -14188,7 +14181,7 @@
       </c>
       <c r="T97" s="26"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20">
       <c r="A98" s="81" t="s">
         <v>183</v>
       </c>
@@ -14235,7 +14228,7 @@
       <c r="S98" s="18"/>
       <c r="T98" s="26"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20">
       <c r="A99" s="81" t="s">
         <v>183</v>
       </c>
@@ -14282,7 +14275,7 @@
       <c r="S99" s="18"/>
       <c r="T99" s="26"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20">
       <c r="A100" s="81" t="s">
         <v>183</v>
       </c>
@@ -14329,7 +14322,7 @@
       <c r="S100" s="18"/>
       <c r="T100" s="26"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20">
       <c r="A101" s="81" t="s">
         <v>230</v>
       </c>
@@ -14376,7 +14369,7 @@
       <c r="S101" s="18"/>
       <c r="T101" s="26"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20">
       <c r="A102" s="81" t="s">
         <v>230</v>
       </c>
@@ -14423,7 +14416,7 @@
       <c r="S102" s="18"/>
       <c r="T102" s="26"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20">
       <c r="A103" s="81" t="s">
         <v>230</v>
       </c>
@@ -14470,7 +14463,7 @@
       <c r="S103" s="18"/>
       <c r="T103" s="26"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20">
       <c r="A104" s="81" t="s">
         <v>230</v>
       </c>
@@ -14517,7 +14510,7 @@
       <c r="S104" s="18"/>
       <c r="T104" s="26"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20">
       <c r="A105" s="81" t="s">
         <v>230</v>
       </c>
@@ -14564,7 +14557,7 @@
       <c r="S105" s="18"/>
       <c r="T105" s="26"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20">
       <c r="A106" s="81" t="s">
         <v>230</v>
       </c>
@@ -14611,7 +14604,7 @@
       <c r="S106" s="18"/>
       <c r="T106" s="26"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20">
       <c r="A107" s="81" t="s">
         <v>230</v>
       </c>
@@ -14658,7 +14651,7 @@
       <c r="S107" s="18"/>
       <c r="T107" s="26"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20">
       <c r="A108" s="81" t="s">
         <v>230</v>
       </c>
@@ -14705,7 +14698,7 @@
       <c r="S108" s="18"/>
       <c r="T108" s="26"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20">
       <c r="A109" s="81" t="s">
         <v>230</v>
       </c>
@@ -14752,7 +14745,7 @@
       <c r="S109" s="18"/>
       <c r="T109" s="26"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20">
       <c r="A110" s="81" t="s">
         <v>230</v>
       </c>
@@ -14799,7 +14792,7 @@
       <c r="S110" s="18"/>
       <c r="T110" s="26"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20">
       <c r="A111" s="81" t="s">
         <v>241</v>
       </c>
@@ -14846,7 +14839,7 @@
       <c r="S111" s="18"/>
       <c r="T111" s="26"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20">
       <c r="A112" s="81" t="s">
         <v>241</v>
       </c>
@@ -14893,7 +14886,7 @@
       <c r="S112" s="18"/>
       <c r="T112" s="26"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20">
       <c r="A113" s="81" t="s">
         <v>241</v>
       </c>
@@ -14940,7 +14933,7 @@
       <c r="S113" s="18"/>
       <c r="T113" s="26"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20">
       <c r="A114" s="81" t="s">
         <v>241</v>
       </c>
@@ -14987,7 +14980,7 @@
       <c r="S114" s="18"/>
       <c r="T114" s="26"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20">
       <c r="A115" s="81" t="s">
         <v>241</v>
       </c>
@@ -15034,7 +15027,7 @@
       <c r="S115" s="18"/>
       <c r="T115" s="26"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20">
       <c r="A116" s="81" t="s">
         <v>241</v>
       </c>
@@ -15081,7 +15074,7 @@
       <c r="S116" s="18"/>
       <c r="T116" s="26"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20">
       <c r="A117" s="81" t="s">
         <v>241</v>
       </c>
@@ -15128,7 +15121,7 @@
       <c r="S117" s="18"/>
       <c r="T117" s="26"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20">
       <c r="A118" s="81" t="s">
         <v>241</v>
       </c>
@@ -15175,7 +15168,7 @@
       <c r="S118" s="18"/>
       <c r="T118" s="26"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20">
       <c r="A119" s="81" t="s">
         <v>241</v>
       </c>
@@ -15222,7 +15215,7 @@
       <c r="S119" s="18"/>
       <c r="T119" s="26"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20">
       <c r="A120" s="81" t="s">
         <v>241</v>
       </c>
@@ -15269,7 +15262,7 @@
       <c r="S120" s="18"/>
       <c r="T120" s="26"/>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20">
       <c r="A121" s="81" t="s">
         <v>241</v>
       </c>
@@ -15316,7 +15309,7 @@
       <c r="S121" s="18"/>
       <c r="T121" s="26"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20">
       <c r="A122" s="81" t="s">
         <v>241</v>
       </c>
@@ -15363,7 +15356,7 @@
       <c r="S122" s="18"/>
       <c r="T122" s="26"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20">
       <c r="A123" s="81" t="s">
         <v>241</v>
       </c>
@@ -15410,7 +15403,7 @@
       <c r="S123" s="18"/>
       <c r="T123" s="26"/>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20">
       <c r="A124" s="81" t="s">
         <v>241</v>
       </c>
@@ -15457,7 +15450,7 @@
       <c r="S124" s="18"/>
       <c r="T124" s="26"/>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20">
       <c r="A125" s="81" t="s">
         <v>241</v>
       </c>
@@ -15504,7 +15497,7 @@
       <c r="S125" s="18"/>
       <c r="T125" s="26"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20">
       <c r="A126" s="81" t="s">
         <v>241</v>
       </c>
@@ -15551,7 +15544,7 @@
       <c r="S126" s="18"/>
       <c r="T126" s="26"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20">
       <c r="A127" s="81"/>
       <c r="B127" s="118"/>
       <c r="C127" s="45"/>
@@ -15576,7 +15569,7 @@
       <c r="S127" s="18"/>
       <c r="T127" s="26"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20">
       <c r="A128" s="81"/>
       <c r="B128" s="118"/>
       <c r="C128" s="45"/>
@@ -15601,7 +15594,7 @@
       <c r="S128" s="18"/>
       <c r="T128" s="26"/>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20">
       <c r="A129" s="81"/>
       <c r="B129" s="118"/>
       <c r="C129" s="45"/>
@@ -15626,7 +15619,7 @@
       <c r="S129" s="18"/>
       <c r="T129" s="26"/>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20">
       <c r="A130" s="81"/>
       <c r="B130" s="118"/>
       <c r="C130" s="45"/>
@@ -15651,7 +15644,7 @@
       <c r="S130" s="18"/>
       <c r="T130" s="26"/>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20">
       <c r="A131" s="81"/>
       <c r="B131" s="118"/>
       <c r="C131" s="45"/>
@@ -15676,7 +15669,7 @@
       <c r="S131" s="18"/>
       <c r="T131" s="26"/>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20">
       <c r="A132" s="81"/>
       <c r="B132" s="118"/>
       <c r="C132" s="45"/>
@@ -15701,7 +15694,7 @@
       <c r="S132" s="18"/>
       <c r="T132" s="26"/>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20">
       <c r="A133" s="81" t="s">
         <v>194</v>
       </c>
@@ -15748,7 +15741,7 @@
       <c r="S133" s="18"/>
       <c r="T133" s="26"/>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20">
       <c r="A134" s="81" t="s">
         <v>196</v>
       </c>
@@ -15795,7 +15788,7 @@
       <c r="S134" s="18"/>
       <c r="T134" s="26"/>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20">
       <c r="A135" s="81" t="s">
         <v>213</v>
       </c>
@@ -15842,7 +15835,7 @@
       <c r="S135" s="18"/>
       <c r="T135" s="26"/>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20">
       <c r="A136" s="81" t="s">
         <v>213</v>
       </c>
@@ -15889,7 +15882,7 @@
       <c r="S136" s="18"/>
       <c r="T136" s="26"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20">
       <c r="A137" s="81" t="s">
         <v>216</v>
       </c>
@@ -15936,7 +15929,7 @@
       <c r="S137" s="18"/>
       <c r="T137" s="26"/>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20">
       <c r="A138" s="81"/>
       <c r="B138" s="118"/>
       <c r="C138" s="45"/>
@@ -15961,7 +15954,7 @@
       <c r="S138" s="18"/>
       <c r="T138" s="26"/>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20">
       <c r="A139" s="81"/>
       <c r="B139" s="118"/>
       <c r="C139" s="45"/>
@@ -15986,7 +15979,7 @@
       <c r="S139" s="18"/>
       <c r="T139" s="26"/>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20">
       <c r="A140" s="114"/>
       <c r="B140" s="78"/>
       <c r="C140" s="30"/>
@@ -16010,7 +16003,7 @@
       <c r="S140" s="18"/>
       <c r="T140" s="26"/>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20">
       <c r="A141" s="114"/>
       <c r="B141" s="78"/>
       <c r="C141" s="30"/>
@@ -16032,7 +16025,7 @@
       <c r="S141" s="18"/>
       <c r="T141" s="26"/>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20">
       <c r="A142" s="114"/>
       <c r="B142" s="78"/>
       <c r="C142" s="30"/>
@@ -16054,7 +16047,7 @@
       <c r="S142" s="18"/>
       <c r="T142" s="26"/>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20">
       <c r="A143" s="114"/>
       <c r="B143" s="78"/>
       <c r="C143" s="30"/>
@@ -16076,7 +16069,7 @@
       <c r="S143" s="18"/>
       <c r="T143" s="26"/>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20">
       <c r="A144" s="70"/>
       <c r="B144" s="79"/>
       <c r="C144" s="79"/>
@@ -16125,7 +16118,7 @@
       <c r="S144" s="26"/>
       <c r="T144" s="26"/>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20">
       <c r="A145" s="81"/>
       <c r="B145" s="118"/>
       <c r="C145" s="45"/>
@@ -16147,7 +16140,7 @@
       <c r="S145" s="18"/>
       <c r="T145" s="26"/>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20">
       <c r="A146" s="81" t="s">
         <v>79</v>
       </c>
@@ -16196,7 +16189,7 @@
       </c>
       <c r="T146" s="26"/>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20">
       <c r="A147" s="81" t="s">
         <v>79</v>
       </c>
@@ -16245,7 +16238,7 @@
       </c>
       <c r="T147" s="26"/>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20">
       <c r="A148" s="81" t="s">
         <v>79</v>
       </c>
@@ -16294,7 +16287,7 @@
       </c>
       <c r="T148" s="26"/>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20">
       <c r="A149" s="81" t="s">
         <v>96</v>
       </c>
@@ -16341,7 +16334,7 @@
       </c>
       <c r="T149" s="26"/>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20">
       <c r="A150" s="81" t="s">
         <v>96</v>
       </c>
@@ -16388,7 +16381,7 @@
       </c>
       <c r="T150" s="26"/>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20">
       <c r="A151" s="81" t="s">
         <v>104</v>
       </c>
@@ -16435,7 +16428,7 @@
       </c>
       <c r="T151" s="26"/>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20">
       <c r="A152" s="81" t="s">
         <v>106</v>
       </c>
@@ -16482,7 +16475,7 @@
       </c>
       <c r="T152" s="26"/>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20">
       <c r="A153" s="81" t="s">
         <v>121</v>
       </c>
@@ -16529,7 +16522,7 @@
       </c>
       <c r="T153" s="26"/>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20">
       <c r="A154" s="81" t="s">
         <v>121</v>
       </c>
@@ -16576,7 +16569,7 @@
       </c>
       <c r="T154" s="26"/>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20">
       <c r="A155" s="81" t="s">
         <v>121</v>
       </c>
@@ -16623,7 +16616,7 @@
       </c>
       <c r="T155" s="26"/>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20">
       <c r="A156" s="81" t="s">
         <v>138</v>
       </c>
@@ -16670,7 +16663,7 @@
       </c>
       <c r="T156" s="26"/>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20">
       <c r="A157" s="81" t="s">
         <v>138</v>
       </c>
@@ -16717,7 +16710,7 @@
       </c>
       <c r="T157" s="26"/>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20">
       <c r="A158" s="81" t="s">
         <v>138</v>
       </c>
@@ -16764,7 +16757,7 @@
       </c>
       <c r="T158" s="26"/>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20">
       <c r="A159" s="81" t="s">
         <v>138</v>
       </c>
@@ -16811,7 +16804,7 @@
       </c>
       <c r="T159" s="26"/>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20">
       <c r="A160" s="81" t="s">
         <v>138</v>
       </c>
@@ -16858,7 +16851,7 @@
       </c>
       <c r="T160" s="26"/>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20">
       <c r="A161" s="81" t="s">
         <v>138</v>
       </c>
@@ -16905,7 +16898,7 @@
       </c>
       <c r="T161" s="26"/>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20">
       <c r="A162" s="81" t="s">
         <v>138</v>
       </c>
@@ -16952,7 +16945,7 @@
       </c>
       <c r="T162" s="26"/>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20">
       <c r="A163" s="81" t="s">
         <v>138</v>
       </c>
@@ -16999,7 +16992,7 @@
       </c>
       <c r="T163" s="26"/>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20">
       <c r="A164" s="81" t="s">
         <v>138</v>
       </c>
@@ -17046,7 +17039,7 @@
       </c>
       <c r="T164" s="26"/>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20">
       <c r="A165" s="81" t="s">
         <v>138</v>
       </c>
@@ -17093,7 +17086,7 @@
       </c>
       <c r="T165" s="26"/>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20">
       <c r="A166" s="81" t="s">
         <v>153</v>
       </c>
@@ -17140,7 +17133,7 @@
       </c>
       <c r="T166" s="26"/>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20">
       <c r="A167" s="81" t="s">
         <v>153</v>
       </c>
@@ -17187,7 +17180,7 @@
       </c>
       <c r="T167" s="26"/>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20">
       <c r="A168" s="81"/>
       <c r="B168" s="118"/>
       <c r="C168" s="45"/>
@@ -17209,7 +17202,7 @@
       <c r="S168" s="18"/>
       <c r="T168" s="26"/>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20">
       <c r="A169" s="81" t="s">
         <v>194</v>
       </c>
@@ -17256,7 +17249,7 @@
       </c>
       <c r="T169" s="26"/>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20">
       <c r="A170" s="81" t="s">
         <v>194</v>
       </c>
@@ -17303,7 +17296,7 @@
       </c>
       <c r="T170" s="26"/>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20">
       <c r="A171" s="81" t="s">
         <v>194</v>
       </c>
@@ -17348,7 +17341,7 @@
       </c>
       <c r="T171" s="26"/>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20">
       <c r="A172" s="81" t="s">
         <v>194</v>
       </c>
@@ -17395,7 +17388,7 @@
       </c>
       <c r="T172" s="26"/>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20">
       <c r="A173" s="81" t="s">
         <v>194</v>
       </c>
@@ -17442,7 +17435,7 @@
       </c>
       <c r="T173" s="26"/>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20">
       <c r="A174" s="81" t="s">
         <v>196</v>
       </c>
@@ -17491,7 +17484,7 @@
       </c>
       <c r="T174" s="26"/>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20">
       <c r="A175" s="81" t="s">
         <v>196</v>
       </c>
@@ -17538,7 +17531,7 @@
       </c>
       <c r="T175" s="26"/>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20">
       <c r="A176" s="81" t="s">
         <v>196</v>
       </c>
@@ -17585,7 +17578,7 @@
       </c>
       <c r="T176" s="26"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20">
       <c r="A177" s="81" t="s">
         <v>196</v>
       </c>
@@ -17632,7 +17625,7 @@
       </c>
       <c r="T177" s="26"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20">
       <c r="A178" s="81" t="s">
         <v>196</v>
       </c>
@@ -17679,7 +17672,7 @@
       </c>
       <c r="T178" s="26"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20">
       <c r="A179" s="81" t="s">
         <v>213</v>
       </c>
@@ -17726,7 +17719,7 @@
       </c>
       <c r="T179" s="26"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20">
       <c r="A180" s="81" t="s">
         <v>213</v>
       </c>
@@ -17773,7 +17766,7 @@
       </c>
       <c r="T180" s="26"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20">
       <c r="A181" s="81" t="s">
         <v>213</v>
       </c>
@@ -17820,7 +17813,7 @@
       </c>
       <c r="T181" s="26"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20">
       <c r="A182" s="81" t="s">
         <v>213</v>
       </c>
@@ -17867,7 +17860,7 @@
       </c>
       <c r="T182" s="26"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20">
       <c r="A183" s="81" t="s">
         <v>213</v>
       </c>
@@ -17914,7 +17907,7 @@
       </c>
       <c r="T183" s="26"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20">
       <c r="A184" s="81" t="s">
         <v>213</v>
       </c>
@@ -17961,7 +17954,7 @@
       </c>
       <c r="T184" s="26"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20">
       <c r="A185" s="81" t="s">
         <v>213</v>
       </c>
@@ -18008,7 +18001,7 @@
       </c>
       <c r="T185" s="26"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20">
       <c r="A186" s="81" t="s">
         <v>232</v>
       </c>
@@ -18055,7 +18048,7 @@
       </c>
       <c r="T186" s="26"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20">
       <c r="A187" s="81" t="s">
         <v>232</v>
       </c>
@@ -18102,7 +18095,7 @@
       </c>
       <c r="T187" s="26"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20">
       <c r="A188" s="81" t="s">
         <v>232</v>
       </c>
@@ -18149,7 +18142,7 @@
       </c>
       <c r="T188" s="26"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20">
       <c r="A189" s="81" t="s">
         <v>232</v>
       </c>
@@ -18196,7 +18189,7 @@
       </c>
       <c r="T189" s="26"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20">
       <c r="A190" s="81" t="s">
         <v>232</v>
       </c>
@@ -18243,7 +18236,7 @@
       </c>
       <c r="T190" s="26"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20">
       <c r="A191" s="81" t="s">
         <v>232</v>
       </c>
@@ -18290,7 +18283,7 @@
       </c>
       <c r="T191" s="26"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20">
       <c r="A192" s="81" t="s">
         <v>244</v>
       </c>
@@ -18337,7 +18330,7 @@
       </c>
       <c r="T192" s="26"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20">
       <c r="A193" s="81" t="s">
         <v>244</v>
       </c>
@@ -18384,7 +18377,7 @@
       </c>
       <c r="T193" s="26"/>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20">
       <c r="A194" s="81" t="s">
         <v>244</v>
       </c>
@@ -18431,7 +18424,7 @@
       </c>
       <c r="T194" s="26"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20">
       <c r="A195" s="81" t="s">
         <v>244</v>
       </c>
@@ -18478,7 +18471,7 @@
       </c>
       <c r="T195" s="26"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20">
       <c r="A196" s="81" t="s">
         <v>244</v>
       </c>
@@ -18525,7 +18518,7 @@
       </c>
       <c r="T196" s="26"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20">
       <c r="A197" s="81" t="s">
         <v>244</v>
       </c>
@@ -18572,7 +18565,7 @@
       </c>
       <c r="T197" s="26"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20">
       <c r="A198" s="81" t="s">
         <v>244</v>
       </c>
@@ -18619,7 +18612,7 @@
       </c>
       <c r="T198" s="26"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20">
       <c r="A199" s="81" t="s">
         <v>244</v>
       </c>
@@ -18666,7 +18659,7 @@
       </c>
       <c r="T199" s="26"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20">
       <c r="A200" s="81"/>
       <c r="B200" s="118"/>
       <c r="C200" s="45"/>
@@ -18688,7 +18681,7 @@
       <c r="S200" s="18"/>
       <c r="T200" s="26"/>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20">
       <c r="A201" s="81"/>
       <c r="B201" s="118"/>
       <c r="C201" s="45"/>
@@ -18710,7 +18703,7 @@
       <c r="S201" s="18"/>
       <c r="T201" s="26"/>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20">
       <c r="A202" s="81"/>
       <c r="B202" s="118"/>
       <c r="C202" s="45"/>
@@ -18732,7 +18725,7 @@
       <c r="S202" s="18"/>
       <c r="T202" s="26"/>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20">
       <c r="A203" s="81" t="s">
         <v>106</v>
       </c>
@@ -18785,7 +18778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20">
       <c r="A204" s="81" t="s">
         <v>106</v>
       </c>
@@ -18838,7 +18831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20">
       <c r="A205" s="81" t="s">
         <v>106</v>
       </c>
@@ -18889,7 +18882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20">
       <c r="A206" s="81" t="s">
         <v>106</v>
       </c>
@@ -18942,7 +18935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20">
       <c r="A207" s="81" t="s">
         <v>106</v>
       </c>
@@ -18995,7 +18988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20">
       <c r="A208" s="81" t="s">
         <v>106</v>
       </c>
@@ -19046,7 +19039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20">
       <c r="A209" s="81" t="s">
         <v>106</v>
       </c>
@@ -19097,7 +19090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20">
       <c r="A210" s="81" t="s">
         <v>106</v>
       </c>
@@ -19148,7 +19141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20">
       <c r="A211" s="81" t="s">
         <v>106</v>
       </c>
@@ -19201,7 +19194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20">
       <c r="A212" s="81" t="s">
         <v>106</v>
       </c>
@@ -19254,7 +19247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20">
       <c r="A213" s="81" t="s">
         <v>106</v>
       </c>
@@ -19307,7 +19300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20">
       <c r="A214" s="81" t="s">
         <v>106</v>
       </c>
@@ -19360,7 +19353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20">
       <c r="A215" s="81" t="s">
         <v>106</v>
       </c>
@@ -19411,7 +19404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20">
       <c r="A216" s="81" t="s">
         <v>106</v>
       </c>
@@ -19462,7 +19455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20">
       <c r="A217" s="81" t="s">
         <v>183</v>
       </c>
@@ -19513,7 +19506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20">
       <c r="A218" s="81" t="s">
         <v>183</v>
       </c>
@@ -19564,7 +19557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20">
       <c r="A219" s="81" t="s">
         <v>183</v>
       </c>
@@ -19615,7 +19608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20">
       <c r="A220" s="81" t="s">
         <v>183</v>
       </c>
@@ -19666,7 +19659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20">
       <c r="A221" s="81" t="s">
         <v>194</v>
       </c>
@@ -19715,7 +19708,7 @@
       </c>
       <c r="T221" s="26"/>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20">
       <c r="A222" s="81" t="s">
         <v>194</v>
       </c>
@@ -19764,7 +19757,7 @@
       </c>
       <c r="T222" s="26"/>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20">
       <c r="A223" s="81" t="s">
         <v>194</v>
       </c>
@@ -19812,7 +19805,7 @@
       </c>
       <c r="T223" s="26"/>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20">
       <c r="A224" s="81" t="s">
         <v>194</v>
       </c>
@@ -19861,7 +19854,7 @@
       </c>
       <c r="T224" s="26"/>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20">
       <c r="A225" s="81" t="s">
         <v>230</v>
       </c>
@@ -19908,7 +19901,7 @@
       <c r="S225" s="18"/>
       <c r="T225" s="26"/>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20">
       <c r="A226" s="81" t="s">
         <v>230</v>
       </c>
@@ -19955,7 +19948,7 @@
       <c r="S226" s="18"/>
       <c r="T226" s="26"/>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20">
       <c r="A227" s="81" t="s">
         <v>230</v>
       </c>
@@ -20002,7 +19995,7 @@
       <c r="S227" s="18"/>
       <c r="T227" s="26"/>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20">
       <c r="A228" s="81" t="s">
         <v>230</v>
       </c>
@@ -20049,7 +20042,7 @@
       <c r="S228" s="18"/>
       <c r="T228" s="26"/>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20">
       <c r="A229" s="81" t="s">
         <v>230</v>
       </c>
@@ -20096,7 +20089,7 @@
       <c r="S229" s="18"/>
       <c r="T229" s="26"/>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20">
       <c r="A230" s="81" t="s">
         <v>230</v>
       </c>
@@ -20143,7 +20136,7 @@
       <c r="S230" s="18"/>
       <c r="T230" s="26"/>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20">
       <c r="A231" s="81" t="s">
         <v>230</v>
       </c>
@@ -20190,7 +20183,7 @@
       <c r="S231" s="18"/>
       <c r="T231" s="26"/>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20">
       <c r="A232" s="81" t="s">
         <v>230</v>
       </c>
@@ -20237,7 +20230,7 @@
       <c r="S232" s="18"/>
       <c r="T232" s="26"/>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20">
       <c r="A233" s="81" t="s">
         <v>230</v>
       </c>
@@ -20284,7 +20277,7 @@
       <c r="S233" s="18"/>
       <c r="T233" s="26"/>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20">
       <c r="A234" s="81" t="s">
         <v>230</v>
       </c>
@@ -20331,7 +20324,7 @@
       <c r="S234" s="18"/>
       <c r="T234" s="26"/>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20">
       <c r="A235" s="81" t="s">
         <v>230</v>
       </c>
@@ -20378,7 +20371,7 @@
       <c r="S235" s="18"/>
       <c r="T235" s="26"/>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20">
       <c r="A236" s="81" t="s">
         <v>230</v>
       </c>
@@ -20425,7 +20418,7 @@
       <c r="S236" s="18"/>
       <c r="T236" s="26"/>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20">
       <c r="A237" s="81" t="s">
         <v>230</v>
       </c>
@@ -20472,7 +20465,7 @@
       <c r="S237" s="18"/>
       <c r="T237" s="26"/>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20">
       <c r="A238" s="81" t="s">
         <v>230</v>
       </c>
@@ -20519,7 +20512,7 @@
       <c r="S238" s="18"/>
       <c r="T238" s="26"/>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20">
       <c r="A239" s="81" t="s">
         <v>230</v>
       </c>
@@ -20566,7 +20559,7 @@
       <c r="S239" s="18"/>
       <c r="T239" s="26"/>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20">
       <c r="A240" s="81" t="s">
         <v>230</v>
       </c>
@@ -20613,7 +20606,7 @@
       <c r="S240" s="18"/>
       <c r="T240" s="26"/>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20">
       <c r="A241" s="81" t="s">
         <v>230</v>
       </c>
@@ -20660,7 +20653,7 @@
       <c r="S241" s="194"/>
       <c r="T241" s="26"/>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20">
       <c r="A242" s="81" t="s">
         <v>241</v>
       </c>
@@ -20707,7 +20700,7 @@
       <c r="S242" s="18"/>
       <c r="T242" s="26"/>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20">
       <c r="A243" s="81" t="s">
         <v>241</v>
       </c>
@@ -20754,7 +20747,7 @@
       <c r="S243" s="18"/>
       <c r="T243" s="26"/>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20">
       <c r="A244" s="81" t="s">
         <v>241</v>
       </c>
@@ -20801,7 +20794,7 @@
       <c r="S244" s="18"/>
       <c r="T244" s="26"/>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20">
       <c r="A245" s="81" t="s">
         <v>241</v>
       </c>
@@ -20848,7 +20841,7 @@
       <c r="S245" s="18"/>
       <c r="T245" s="26"/>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20">
       <c r="A246" s="81" t="s">
         <v>241</v>
       </c>
@@ -20895,7 +20888,7 @@
       <c r="S246" s="18"/>
       <c r="T246" s="26"/>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20">
       <c r="A247" s="81" t="s">
         <v>241</v>
       </c>
@@ -20942,7 +20935,7 @@
       <c r="S247" s="18"/>
       <c r="T247" s="26"/>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20">
       <c r="A248" s="81" t="s">
         <v>241</v>
       </c>
@@ -20989,7 +20982,7 @@
       <c r="S248" s="18"/>
       <c r="T248" s="26"/>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20">
       <c r="A249" s="81" t="s">
         <v>241</v>
       </c>
@@ -21036,7 +21029,7 @@
       <c r="S249" s="18"/>
       <c r="T249" s="26"/>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20">
       <c r="A250" s="81" t="s">
         <v>241</v>
       </c>
@@ -21083,7 +21076,7 @@
       <c r="S250" s="18"/>
       <c r="T250" s="26"/>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20">
       <c r="A251" s="81" t="s">
         <v>241</v>
       </c>
@@ -21130,7 +21123,7 @@
       <c r="S251" s="18"/>
       <c r="T251" s="26"/>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20">
       <c r="A252" s="81" t="s">
         <v>241</v>
       </c>
@@ -21177,7 +21170,7 @@
       <c r="S252" s="18"/>
       <c r="T252" s="26"/>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20">
       <c r="A253" s="81" t="s">
         <v>241</v>
       </c>
@@ -21224,7 +21217,7 @@
       <c r="S253" s="18"/>
       <c r="T253" s="26"/>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20">
       <c r="A254" s="81" t="s">
         <v>241</v>
       </c>
@@ -21271,7 +21264,7 @@
       <c r="S254" s="18"/>
       <c r="T254" s="26"/>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20">
       <c r="A255" s="81" t="s">
         <v>241</v>
       </c>
@@ -21318,7 +21311,7 @@
       <c r="S255" s="18"/>
       <c r="T255" s="26"/>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20">
       <c r="A256" s="81" t="s">
         <v>241</v>
       </c>
@@ -21365,7 +21358,7 @@
       <c r="S256" s="18"/>
       <c r="T256" s="26"/>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20">
       <c r="A257" s="81" t="s">
         <v>241</v>
       </c>
@@ -21412,7 +21405,7 @@
       <c r="S257" s="18"/>
       <c r="T257" s="26"/>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20">
       <c r="A258" s="81" t="s">
         <v>241</v>
       </c>
@@ -21459,7 +21452,7 @@
       <c r="S258" s="18"/>
       <c r="T258" s="26"/>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20">
       <c r="A259" s="81" t="s">
         <v>241</v>
       </c>
@@ -21506,7 +21499,7 @@
       <c r="S259" s="18"/>
       <c r="T259" s="26"/>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20">
       <c r="A260" s="81"/>
       <c r="B260" s="118"/>
       <c r="C260" s="45"/>
@@ -21531,7 +21524,7 @@
       <c r="S260" s="18"/>
       <c r="T260" s="26"/>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20">
       <c r="A261" s="81"/>
       <c r="B261" s="118"/>
       <c r="C261" s="45"/>
@@ -21556,7 +21549,7 @@
       <c r="S261" s="18"/>
       <c r="T261" s="26"/>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20">
       <c r="A262" s="81"/>
       <c r="B262" s="118"/>
       <c r="C262" s="45"/>
@@ -21581,7 +21574,7 @@
       <c r="S262" s="18"/>
       <c r="T262" s="26"/>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20">
       <c r="A263" s="81"/>
       <c r="B263" s="118"/>
       <c r="C263" s="45"/>
@@ -21606,7 +21599,7 @@
       <c r="S263" s="18"/>
       <c r="T263" s="26"/>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20">
       <c r="A264" s="81"/>
       <c r="B264" s="118"/>
       <c r="C264" s="45"/>
@@ -21631,7 +21624,7 @@
       <c r="S264" s="18"/>
       <c r="T264" s="26"/>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20">
       <c r="A265" s="81" t="s">
         <v>194</v>
       </c>
@@ -21678,7 +21671,7 @@
       <c r="S265" s="18"/>
       <c r="T265" s="26"/>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20">
       <c r="A266" s="81" t="s">
         <v>194</v>
       </c>
@@ -21725,7 +21718,7 @@
       <c r="S266" s="18"/>
       <c r="T266" s="26"/>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20">
       <c r="A267" s="81" t="s">
         <v>194</v>
       </c>
@@ -21772,7 +21765,7 @@
       <c r="S267" s="18"/>
       <c r="T267" s="26"/>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20">
       <c r="A268" s="81" t="s">
         <v>194</v>
       </c>
@@ -21819,7 +21812,7 @@
       <c r="S268" s="18"/>
       <c r="T268" s="26"/>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20">
       <c r="A269" s="81" t="s">
         <v>196</v>
       </c>
@@ -21866,7 +21859,7 @@
       <c r="S269" s="18"/>
       <c r="T269" s="26"/>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20">
       <c r="A270" s="81" t="s">
         <v>196</v>
       </c>
@@ -21913,7 +21906,7 @@
       <c r="S270" s="18"/>
       <c r="T270" s="26"/>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20">
       <c r="A271" s="81" t="s">
         <v>196</v>
       </c>
@@ -21960,7 +21953,7 @@
       <c r="S271" s="18"/>
       <c r="T271" s="26"/>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20">
       <c r="A272" s="81" t="s">
         <v>196</v>
       </c>
@@ -22007,7 +22000,7 @@
       <c r="S272" s="18"/>
       <c r="T272" s="26"/>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20">
       <c r="A273" s="81" t="s">
         <v>213</v>
       </c>
@@ -22054,7 +22047,7 @@
       <c r="S273" s="18"/>
       <c r="T273" s="26"/>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20">
       <c r="A274" s="81" t="s">
         <v>213</v>
       </c>
@@ -22101,7 +22094,7 @@
       <c r="S274" s="18"/>
       <c r="T274" s="26"/>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20">
       <c r="A275" s="81" t="s">
         <v>213</v>
       </c>
@@ -22148,7 +22141,7 @@
       <c r="S275" s="18"/>
       <c r="T275" s="26"/>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20">
       <c r="A276" s="81" t="s">
         <v>213</v>
       </c>
@@ -22195,7 +22188,7 @@
       <c r="S276" s="18"/>
       <c r="T276" s="26"/>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20">
       <c r="A277" s="81" t="s">
         <v>213</v>
       </c>
@@ -22242,7 +22235,7 @@
       <c r="S277" s="18"/>
       <c r="T277" s="26"/>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20">
       <c r="A278" s="81" t="s">
         <v>213</v>
       </c>
@@ -22289,7 +22282,7 @@
       <c r="S278" s="18"/>
       <c r="T278" s="26"/>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20">
       <c r="A279" s="81" t="s">
         <v>213</v>
       </c>
@@ -22336,7 +22329,7 @@
       <c r="S279" s="18"/>
       <c r="T279" s="26"/>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20">
       <c r="A280" s="81" t="s">
         <v>213</v>
       </c>
@@ -22383,7 +22376,7 @@
       <c r="S280" s="18"/>
       <c r="T280" s="26"/>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20">
       <c r="A281" s="81" t="s">
         <v>213</v>
       </c>
@@ -22430,7 +22423,7 @@
       <c r="S281" s="18"/>
       <c r="T281" s="26"/>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20">
       <c r="A282" s="81" t="s">
         <v>216</v>
       </c>
@@ -22477,7 +22470,7 @@
       <c r="S282" s="18"/>
       <c r="T282" s="26"/>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20">
       <c r="A283" s="81" t="s">
         <v>216</v>
       </c>
@@ -22524,7 +22517,7 @@
       <c r="S283" s="18"/>
       <c r="T283" s="26"/>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20">
       <c r="A284" s="81" t="s">
         <v>216</v>
       </c>
@@ -22571,7 +22564,7 @@
       <c r="S284" s="18"/>
       <c r="T284" s="26"/>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20">
       <c r="A285" s="81" t="s">
         <v>216</v>
       </c>
@@ -22618,7 +22611,7 @@
       <c r="S285" s="18"/>
       <c r="T285" s="26"/>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20">
       <c r="A286" s="81" t="s">
         <v>216</v>
       </c>
@@ -22665,7 +22658,7 @@
       <c r="S286" s="18"/>
       <c r="T286" s="26"/>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20">
       <c r="A287" s="81" t="s">
         <v>216</v>
       </c>
@@ -22712,7 +22705,7 @@
       <c r="S287" s="18"/>
       <c r="T287" s="26"/>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20">
       <c r="A288" s="81" t="s">
         <v>216</v>
       </c>
@@ -22759,7 +22752,7 @@
       <c r="S288" s="18"/>
       <c r="T288" s="26"/>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20">
       <c r="A289" s="81" t="s">
         <v>216</v>
       </c>
@@ -22806,7 +22799,7 @@
       <c r="S289" s="18"/>
       <c r="T289" s="26"/>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20">
       <c r="A290" s="81" t="s">
         <v>216</v>
       </c>
@@ -22853,7 +22846,7 @@
       <c r="S290" s="18"/>
       <c r="T290" s="26"/>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20">
       <c r="A291" s="81" t="s">
         <v>216</v>
       </c>
@@ -22900,7 +22893,7 @@
       <c r="S291" s="18"/>
       <c r="T291" s="26"/>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20">
       <c r="A292" s="81" t="s">
         <v>216</v>
       </c>
@@ -22947,7 +22940,7 @@
       <c r="S292" s="18"/>
       <c r="T292" s="26"/>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20">
       <c r="A293" s="81"/>
       <c r="B293" s="118"/>
       <c r="C293" s="45"/>
@@ -22969,7 +22962,7 @@
       <c r="S293" s="18"/>
       <c r="T293" s="26"/>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20">
       <c r="A294" s="34"/>
       <c r="B294" s="35"/>
       <c r="C294" s="35"/>
@@ -22993,7 +22986,7 @@
       <c r="S294" s="18"/>
       <c r="T294" s="26"/>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20">
       <c r="A295" s="34"/>
       <c r="B295" s="35"/>
       <c r="C295" s="35"/>
@@ -23015,7 +23008,7 @@
       <c r="S295" s="29"/>
       <c r="T295" s="26"/>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20">
       <c r="A296" s="34"/>
       <c r="B296" s="35"/>
       <c r="C296" s="35"/>
@@ -23039,7 +23032,7 @@
       <c r="S296" s="29"/>
       <c r="T296" s="26"/>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20">
       <c r="A297" s="34"/>
       <c r="B297" s="35"/>
       <c r="C297" s="35"/>
@@ -23063,7 +23056,7 @@
       <c r="S297" s="29"/>
       <c r="T297" s="26"/>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20">
       <c r="A298" s="34"/>
       <c r="B298" s="35"/>
       <c r="C298" s="35"/>
@@ -23089,7 +23082,7 @@
       <c r="S298" s="29"/>
       <c r="T298" s="26"/>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20">
       <c r="A299" s="34"/>
       <c r="B299" s="35"/>
       <c r="C299" s="35"/>
@@ -23115,7 +23108,7 @@
       <c r="S299" s="29"/>
       <c r="T299" s="26"/>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20">
       <c r="A300" s="34"/>
       <c r="B300" s="35"/>
       <c r="C300" s="35"/>
@@ -23137,7 +23130,7 @@
       <c r="S300" s="29"/>
       <c r="T300" s="26"/>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20">
       <c r="A301" s="70"/>
       <c r="B301" s="131"/>
       <c r="C301" s="70"/>
@@ -23186,7 +23179,7 @@
       <c r="S301" s="26"/>
       <c r="T301" s="26"/>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20">
       <c r="A302" s="81"/>
       <c r="B302" s="118"/>
       <c r="C302" s="45"/>
@@ -23211,7 +23204,7 @@
       <c r="S302" s="18"/>
       <c r="T302" s="94"/>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20">
       <c r="A303" s="81"/>
       <c r="B303" s="118"/>
       <c r="C303" s="45"/>
@@ -23236,7 +23229,7 @@
       <c r="S303" s="18"/>
       <c r="T303" s="94"/>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20">
       <c r="A304" s="81"/>
       <c r="B304" s="118"/>
       <c r="C304" s="45"/>
@@ -23261,7 +23254,7 @@
       <c r="S304" s="18"/>
       <c r="T304" s="94"/>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20">
       <c r="A305" s="81" t="s">
         <v>164</v>
       </c>
@@ -23312,7 +23305,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20">
       <c r="A306" s="81" t="s">
         <v>164</v>
       </c>
@@ -23363,7 +23356,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20">
       <c r="A307" s="81" t="s">
         <v>164</v>
       </c>
@@ -23414,7 +23407,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20">
       <c r="A308" s="81" t="s">
         <v>161</v>
       </c>
@@ -23459,7 +23452,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20">
       <c r="A309" s="81"/>
       <c r="B309" s="118"/>
       <c r="C309" s="45"/>
@@ -23481,7 +23474,7 @@
       <c r="S309" s="18"/>
       <c r="T309" s="94"/>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20">
       <c r="A310" s="81" t="s">
         <v>194</v>
       </c>
@@ -23522,7 +23515,7 @@
       <c r="S310" s="18"/>
       <c r="T310" s="94"/>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20">
       <c r="A311" s="81" t="s">
         <v>194</v>
       </c>
@@ -23563,7 +23556,7 @@
       <c r="S311" s="18"/>
       <c r="T311" s="94"/>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20">
       <c r="A312" s="81" t="s">
         <v>194</v>
       </c>
@@ -23604,7 +23597,7 @@
       <c r="S312" s="18"/>
       <c r="T312" s="94"/>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20">
       <c r="A313" s="81" t="s">
         <v>230</v>
       </c>
@@ -23655,7 +23648,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20">
       <c r="A314" s="81" t="s">
         <v>230</v>
       </c>
@@ -23706,7 +23699,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20">
       <c r="A315" s="81" t="s">
         <v>241</v>
       </c>
@@ -23757,7 +23750,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20">
       <c r="A316" s="81" t="s">
         <v>241</v>
       </c>
@@ -23808,7 +23801,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20">
       <c r="A317" s="81" t="s">
         <v>241</v>
       </c>
@@ -23859,7 +23852,7 @@
         <v>0.215</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20">
       <c r="A318" s="81" t="s">
         <v>241</v>
       </c>
@@ -23910,7 +23903,7 @@
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20">
       <c r="A319" s="81" t="s">
         <v>241</v>
       </c>
@@ -23961,7 +23954,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20">
       <c r="A320" s="81"/>
       <c r="B320" s="118"/>
       <c r="C320" s="45"/>
@@ -23986,7 +23979,7 @@
       <c r="S320" s="18"/>
       <c r="T320" s="94"/>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20">
       <c r="A321" s="81"/>
       <c r="B321" s="118"/>
       <c r="C321" s="45"/>
@@ -24011,7 +24004,7 @@
       <c r="S321" s="18"/>
       <c r="T321" s="94"/>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20">
       <c r="A322" s="81" t="s">
         <v>196</v>
       </c>
@@ -24062,7 +24055,7 @@
         <v>0.16900000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20">
       <c r="A323" s="81" t="s">
         <v>213</v>
       </c>
@@ -24113,7 +24106,7 @@
         <v>0.16900000000000001</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20">
       <c r="A324" s="81" t="s">
         <v>213</v>
       </c>
@@ -24164,7 +24157,7 @@
         <v>0.16900000000000001</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20">
       <c r="A325" s="81" t="s">
         <v>213</v>
       </c>
@@ -24215,7 +24208,7 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20">
       <c r="A326" s="81" t="s">
         <v>216</v>
       </c>
@@ -24266,7 +24259,7 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20">
       <c r="A327" s="81" t="s">
         <v>216</v>
       </c>
@@ -24317,7 +24310,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20">
       <c r="A328" s="81" t="s">
         <v>216</v>
       </c>
@@ -24368,7 +24361,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20">
       <c r="A329" s="81"/>
       <c r="B329" s="118"/>
       <c r="C329" s="45"/>
@@ -24390,7 +24383,7 @@
       <c r="S329" s="18"/>
       <c r="T329" s="94"/>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20">
       <c r="A330" s="81" t="s">
         <v>196</v>
       </c>
@@ -24433,7 +24426,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20">
       <c r="A331" s="81" t="s">
         <v>196</v>
       </c>
@@ -24476,7 +24469,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20">
       <c r="A332" s="81" t="s">
         <v>196</v>
       </c>
@@ -24519,7 +24512,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20">
       <c r="A333" s="81" t="s">
         <v>216</v>
       </c>
@@ -24560,7 +24553,7 @@
       </c>
       <c r="T333" s="94"/>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20">
       <c r="A334" s="81" t="s">
         <v>216</v>
       </c>
@@ -24601,7 +24594,7 @@
       </c>
       <c r="T334" s="94"/>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20">
       <c r="A335" s="81" t="s">
         <v>216</v>
       </c>
@@ -24642,7 +24635,7 @@
       </c>
       <c r="T335" s="94"/>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20">
       <c r="A336" s="81"/>
       <c r="B336" s="118"/>
       <c r="C336" s="45"/>
@@ -24664,7 +24657,7 @@
       <c r="S336" s="18"/>
       <c r="T336" s="94"/>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20">
       <c r="A337" s="81"/>
       <c r="B337" s="118"/>
       <c r="C337" s="45"/>
@@ -24689,7 +24682,7 @@
       <c r="S337" s="18"/>
       <c r="T337" s="94"/>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20">
       <c r="A338" s="124"/>
       <c r="B338" s="133"/>
       <c r="C338" s="125"/>
@@ -24711,7 +24704,7 @@
       <c r="S338" s="18"/>
       <c r="T338" s="18"/>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20">
       <c r="A339" s="124"/>
       <c r="B339" s="133"/>
       <c r="C339" s="125"/>
@@ -24733,7 +24726,7 @@
       <c r="S339" s="18"/>
       <c r="T339" s="18"/>
     </row>
-    <row r="340" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" ht="16">
       <c r="A340" s="124"/>
       <c r="B340" s="133"/>
       <c r="C340" s="125"/>
@@ -24755,7 +24748,7 @@
       <c r="S340" s="18"/>
       <c r="T340" s="18"/>
     </row>
-    <row r="341" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" ht="16">
       <c r="A341" s="124"/>
       <c r="B341" s="133"/>
       <c r="C341" s="125"/>
@@ -24783,7 +24776,7 @@
       <c r="S341" s="18"/>
       <c r="T341" s="18"/>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20">
       <c r="A342" s="124"/>
       <c r="B342" s="133"/>
       <c r="C342" s="125"/>
@@ -24805,7 +24798,7 @@
       <c r="S342" s="18"/>
       <c r="T342" s="18"/>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20">
       <c r="A343" s="124"/>
       <c r="B343" s="133"/>
       <c r="C343" s="125"/>
@@ -24827,7 +24820,7 @@
       <c r="S343" s="18"/>
       <c r="T343" s="18"/>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20">
       <c r="A344" s="127"/>
       <c r="B344" s="134"/>
       <c r="C344" s="125"/>
@@ -24849,7 +24842,7 @@
       <c r="S344" s="18"/>
       <c r="T344" s="18"/>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20">
       <c r="A345" s="128"/>
       <c r="B345" s="135"/>
       <c r="C345" s="129"/>
@@ -24898,7 +24891,7 @@
       <c r="S345" s="18"/>
       <c r="T345" s="18"/>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20">
       <c r="A346" s="128" t="s">
         <v>196</v>
       </c>
@@ -24937,7 +24930,7 @@
       <c r="S346" s="18"/>
       <c r="T346" s="18"/>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20">
       <c r="A347" s="128" t="s">
         <v>196</v>
       </c>
@@ -24976,7 +24969,7 @@
       <c r="S347" s="18"/>
       <c r="T347" s="18"/>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20">
       <c r="A348" s="128" t="s">
         <v>216</v>
       </c>
@@ -25023,7 +25016,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20">
       <c r="A349" s="128" t="s">
         <v>216</v>
       </c>
@@ -25070,7 +25063,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20">
       <c r="A350" s="128"/>
       <c r="B350" s="135"/>
       <c r="C350" s="129"/>
@@ -25095,7 +25088,7 @@
       <c r="S350" s="18"/>
       <c r="T350" s="18"/>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20">
       <c r="A351" s="70"/>
       <c r="B351" s="131"/>
       <c r="C351" s="70"/>
@@ -25144,7 +25137,7 @@
       <c r="S351" s="26"/>
       <c r="T351" s="26"/>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20">
       <c r="A352" s="70"/>
       <c r="B352" s="131"/>
       <c r="C352" s="81"/>
@@ -25166,7 +25159,7 @@
       <c r="S352" s="26"/>
       <c r="T352" s="26"/>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20">
       <c r="A353" s="70"/>
       <c r="B353" s="131"/>
       <c r="C353" s="70"/>
@@ -25188,14 +25181,14 @@
       <c r="S353" s="26"/>
       <c r="T353" s="70"/>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20">
       <c r="A354" s="70"/>
       <c r="B354" s="131"/>
       <c r="C354" s="70"/>
-      <c r="D354" s="202" t="s">
+      <c r="D354" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="E354" s="203"/>
+      <c r="E354" s="214"/>
       <c r="F354" s="39">
         <f>SUM(F28,F144,F301,F345,F351)</f>
         <v>267587</v>
@@ -25235,7 +25228,7 @@
       <c r="S354" s="26"/>
       <c r="T354" s="70"/>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20">
       <c r="A355" s="111"/>
       <c r="B355" s="111"/>
       <c r="C355" s="111"/>
@@ -25257,7 +25250,7 @@
       <c r="S355" s="116"/>
       <c r="T355" s="111"/>
     </row>
-    <row r="356" spans="1:20" ht="18" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" ht="18">
       <c r="A356" s="111"/>
       <c r="B356" s="111"/>
       <c r="C356" s="111"/>
@@ -25302,54 +25295,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC20C82-34A3-4FB4-A98E-B79CCA462071}">
   <sheetPr codeName="Foglio5"/>
   <dimension ref="A1:U64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="15" max="15" width="9.85546875" customWidth="1"/>
+    <col min="13" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="15" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
+    <row r="1" spans="1:21" ht="26" thickBot="1">
+      <c r="A1" s="227" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
       <c r="D1" s="1">
         <v>46195</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="228" t="s">
+      <c r="G1" s="230" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-    </row>
-    <row r="2" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
+    </row>
+    <row r="2" spans="1:21" ht="16" thickTop="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="42">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -25412,7 +25404,7 @@
       </c>
       <c r="U3" s="138"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21">
       <c r="A4" s="188" t="s">
         <v>170</v>
       </c>
@@ -25464,7 +25456,7 @@
       </c>
       <c r="U4" s="119"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21">
       <c r="A5" s="188" t="s">
         <v>170</v>
       </c>
@@ -25516,7 +25508,7 @@
       </c>
       <c r="U5" s="119"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21">
       <c r="A6" s="19"/>
       <c r="B6" s="74"/>
       <c r="C6" s="96"/>
@@ -25539,7 +25531,7 @@
       <c r="T6" s="13"/>
       <c r="U6" s="119"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21">
       <c r="A7" s="19"/>
       <c r="B7" s="74"/>
       <c r="C7" s="96"/>
@@ -25562,7 +25554,7 @@
       <c r="T7" s="13"/>
       <c r="U7" s="119"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21">
       <c r="A8" s="112"/>
       <c r="B8" s="96"/>
       <c r="C8" s="99"/>
@@ -25585,7 +25577,7 @@
       <c r="T8" s="13"/>
       <c r="U8" s="119"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21">
       <c r="A9" s="112"/>
       <c r="B9" s="112"/>
       <c r="C9" s="99"/>
@@ -25608,7 +25600,7 @@
       <c r="T9" s="13"/>
       <c r="U9" s="119"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21">
       <c r="A10" s="112"/>
       <c r="B10" s="112"/>
       <c r="C10" s="99"/>
@@ -25631,7 +25623,7 @@
       <c r="T10" s="13"/>
       <c r="U10" s="119"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="A11" s="160"/>
       <c r="B11" s="116"/>
       <c r="C11" s="92"/>
@@ -25681,7 +25673,7 @@
       <c r="T11" s="26"/>
       <c r="U11" s="119"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21">
       <c r="A12" s="188" t="s">
         <v>170</v>
       </c>
@@ -25733,7 +25725,7 @@
       </c>
       <c r="U12" s="119"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="A13" s="188" t="s">
         <v>170</v>
       </c>
@@ -25785,7 +25777,7 @@
       </c>
       <c r="U13" s="119"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21">
       <c r="A14" s="188" t="s">
         <v>170</v>
       </c>
@@ -25837,7 +25829,7 @@
       </c>
       <c r="U14" s="119"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="A15" s="188" t="s">
         <v>170</v>
       </c>
@@ -25889,7 +25881,7 @@
       </c>
       <c r="U15" s="119"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="A16" s="188" t="s">
         <v>170</v>
       </c>
@@ -25941,7 +25933,7 @@
       </c>
       <c r="U16" s="119"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21">
       <c r="A17" s="188" t="s">
         <v>170</v>
       </c>
@@ -25993,7 +25985,7 @@
       </c>
       <c r="U17" s="119"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21">
       <c r="A18" s="188" t="s">
         <v>170</v>
       </c>
@@ -26045,7 +26037,7 @@
       </c>
       <c r="U18" s="119"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21">
       <c r="A19" s="188" t="s">
         <v>170</v>
       </c>
@@ -26097,7 +26089,7 @@
       </c>
       <c r="U19" s="119"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21">
       <c r="A20" s="188" t="s">
         <v>170</v>
       </c>
@@ -26149,7 +26141,7 @@
       </c>
       <c r="U20" s="119"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21">
       <c r="A21" s="114"/>
       <c r="B21" s="78"/>
       <c r="C21" s="30"/>
@@ -26172,7 +26164,7 @@
       <c r="T21" s="26"/>
       <c r="U21" s="119"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21">
       <c r="A22" s="114"/>
       <c r="B22" s="78"/>
       <c r="C22" s="78"/>
@@ -26195,7 +26187,7 @@
       <c r="T22" s="26"/>
       <c r="U22" s="119"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21">
       <c r="A23" s="70"/>
       <c r="B23" s="79"/>
       <c r="C23" s="79"/>
@@ -26245,7 +26237,7 @@
       <c r="T23" s="26"/>
       <c r="U23" s="119"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21">
       <c r="A24" s="188" t="s">
         <v>170</v>
       </c>
@@ -26297,7 +26289,7 @@
       </c>
       <c r="U24" s="119"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21">
       <c r="A25" s="188" t="s">
         <v>170</v>
       </c>
@@ -26349,7 +26341,7 @@
       </c>
       <c r="U25" s="119"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21">
       <c r="A26" s="188" t="s">
         <v>170</v>
       </c>
@@ -26401,7 +26393,7 @@
       </c>
       <c r="U26" s="119"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21">
       <c r="A27" s="188" t="s">
         <v>170</v>
       </c>
@@ -26453,7 +26445,7 @@
       </c>
       <c r="U27" s="119"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21">
       <c r="A28" s="188" t="s">
         <v>170</v>
       </c>
@@ -26505,7 +26497,7 @@
       </c>
       <c r="U28" s="119"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21">
       <c r="A29" s="188" t="s">
         <v>170</v>
       </c>
@@ -26557,7 +26549,7 @@
       </c>
       <c r="U29" s="119"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21">
       <c r="A30" s="188" t="s">
         <v>170</v>
       </c>
@@ -26609,7 +26601,7 @@
       </c>
       <c r="U30" s="119"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21">
       <c r="A31" s="188" t="s">
         <v>170</v>
       </c>
@@ -26661,7 +26653,7 @@
       </c>
       <c r="U31" s="119"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21">
       <c r="A32" s="188" t="s">
         <v>170</v>
       </c>
@@ -26713,7 +26705,7 @@
       </c>
       <c r="U32" s="119"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21">
       <c r="A33" s="188" t="s">
         <v>170</v>
       </c>
@@ -26765,7 +26757,7 @@
       </c>
       <c r="U33" s="119"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21">
       <c r="A34" s="34"/>
       <c r="B34" s="35"/>
       <c r="C34" s="35"/>
@@ -26788,7 +26780,7 @@
       <c r="T34" s="26"/>
       <c r="U34" s="119"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21">
       <c r="A35" s="34"/>
       <c r="B35" s="35"/>
       <c r="C35" s="35"/>
@@ -26811,7 +26803,7 @@
       <c r="T35" s="26"/>
       <c r="U35" s="119"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21">
       <c r="A36" s="34"/>
       <c r="B36" s="35"/>
       <c r="C36" s="80"/>
@@ -26834,7 +26826,7 @@
       <c r="T36" s="26"/>
       <c r="U36" s="119"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21">
       <c r="A37" s="70"/>
       <c r="B37" s="131"/>
       <c r="C37" s="70"/>
@@ -26884,7 +26876,7 @@
       <c r="T37" s="26"/>
       <c r="U37" s="119"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21">
       <c r="A38" s="188"/>
       <c r="B38" s="92"/>
       <c r="C38" s="161"/>
@@ -26907,7 +26899,7 @@
       <c r="T38" s="94"/>
       <c r="U38" s="123"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21">
       <c r="A39" s="188"/>
       <c r="B39" s="92"/>
       <c r="C39" s="161"/>
@@ -26930,7 +26922,7 @@
       <c r="T39" s="94"/>
       <c r="U39" s="123"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21">
       <c r="A40" s="124"/>
       <c r="B40" s="133"/>
       <c r="C40" s="125"/>
@@ -26953,7 +26945,7 @@
       <c r="T40" s="18"/>
       <c r="U40" s="122"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21">
       <c r="A41" s="124"/>
       <c r="B41" s="133"/>
       <c r="C41" s="125"/>
@@ -26976,7 +26968,7 @@
       <c r="T41" s="18"/>
       <c r="U41" s="122"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21">
       <c r="A42" s="127"/>
       <c r="B42" s="134"/>
       <c r="C42" s="125"/>
@@ -26999,7 +26991,7 @@
       <c r="T42" s="18"/>
       <c r="U42" s="123"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21">
       <c r="A43" s="128"/>
       <c r="B43" s="135"/>
       <c r="C43" s="129"/>
@@ -27049,7 +27041,7 @@
       <c r="T43" s="18"/>
       <c r="U43" s="123"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21">
       <c r="A44" s="70"/>
       <c r="B44" s="131"/>
       <c r="C44" s="70"/>
@@ -27072,14 +27064,14 @@
       <c r="T44" s="70"/>
       <c r="U44" s="111"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21">
       <c r="A45" s="70"/>
       <c r="B45" s="131"/>
       <c r="C45" s="70"/>
-      <c r="D45" s="202" t="s">
+      <c r="D45" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="203"/>
+      <c r="E45" s="214"/>
       <c r="F45" s="39">
         <f>SUM(F11,F23,F37,F43,)</f>
         <v>20414</v>
@@ -27120,7 +27112,7 @@
       <c r="T45" s="70"/>
       <c r="U45" s="111"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21">
       <c r="A46" s="111"/>
       <c r="B46" s="111"/>
       <c r="C46" s="111"/>
@@ -27143,7 +27135,7 @@
       <c r="T46" s="111"/>
       <c r="U46" s="111"/>
     </row>
-    <row r="47" spans="1:21" ht="18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="18">
       <c r="A47" s="111"/>
       <c r="B47" s="111"/>
       <c r="C47" s="111"/>
@@ -27171,7 +27163,7 @@
       <c r="T47" s="111"/>
       <c r="U47" s="111"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21">
       <c r="A48" s="111"/>
       <c r="B48" s="111"/>
       <c r="C48" s="111"/>
@@ -27194,7 +27186,7 @@
       <c r="T48" s="111"/>
       <c r="U48" s="111"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21">
       <c r="A49" s="111"/>
       <c r="B49" s="111"/>
       <c r="C49" s="111"/>
@@ -27217,7 +27209,7 @@
       <c r="T49" s="111"/>
       <c r="U49" s="111"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21">
       <c r="A50" s="111"/>
       <c r="B50" s="111"/>
       <c r="C50" s="111"/>
@@ -27240,7 +27232,7 @@
       <c r="T50" s="111"/>
       <c r="U50" s="111"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21">
       <c r="A51" s="111"/>
       <c r="B51" s="111"/>
       <c r="C51" s="111"/>
@@ -27263,7 +27255,7 @@
       <c r="T51" s="111"/>
       <c r="U51" s="111"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21">
       <c r="A52" s="111"/>
       <c r="B52" s="111"/>
       <c r="C52" s="111"/>
@@ -27286,7 +27278,7 @@
       <c r="T52" s="111"/>
       <c r="U52" s="111"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21">
       <c r="A53" s="111"/>
       <c r="B53" s="111"/>
       <c r="C53" s="111"/>
@@ -27309,22 +27301,22 @@
       <c r="T53" s="111"/>
       <c r="U53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="33" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:21" ht="33">
       <c r="A54" s="111"/>
       <c r="B54" s="111"/>
       <c r="C54" s="111"/>
-      <c r="D54" s="220" t="s">
+      <c r="D54" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="221"/>
-      <c r="F54" s="221"/>
-      <c r="G54" s="221"/>
-      <c r="H54" s="221"/>
-      <c r="I54" s="221"/>
-      <c r="J54" s="221"/>
-      <c r="K54" s="221"/>
-      <c r="L54" s="221"/>
-      <c r="M54" s="222"/>
+      <c r="E54" s="216"/>
+      <c r="F54" s="216"/>
+      <c r="G54" s="216"/>
+      <c r="H54" s="216"/>
+      <c r="I54" s="216"/>
+      <c r="J54" s="216"/>
+      <c r="K54" s="216"/>
+      <c r="L54" s="216"/>
+      <c r="M54" s="217"/>
       <c r="N54" s="111"/>
       <c r="O54" s="111"/>
       <c r="P54" s="111"/>
@@ -27334,7 +27326,7 @@
       <c r="T54" s="111"/>
       <c r="U54" s="111"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21">
       <c r="A55" s="111"/>
       <c r="B55" s="111"/>
       <c r="C55" s="111"/>
@@ -27357,7 +27349,7 @@
       <c r="T55" s="111"/>
       <c r="U55" s="111"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21">
       <c r="A56" s="111"/>
       <c r="B56" s="111"/>
       <c r="C56" s="111"/>
@@ -27380,12 +27372,12 @@
       <c r="T56" s="111"/>
       <c r="U56" s="111"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="223" t="s">
+    <row r="57" spans="1:21">
+      <c r="A57" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="224"/>
-      <c r="C57" s="225"/>
+      <c r="B57" s="204"/>
+      <c r="C57" s="205"/>
       <c r="D57" s="44" t="s">
         <v>26</v>
       </c>
@@ -27395,14 +27387,14 @@
       <c r="F57" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="G57" s="223" t="s">
+      <c r="G57" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="225"/>
-      <c r="I57" s="223" t="s">
+      <c r="H57" s="205"/>
+      <c r="I57" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="J57" s="225"/>
+      <c r="J57" s="205"/>
       <c r="K57" s="111"/>
       <c r="L57" s="111"/>
       <c r="M57" s="111"/>
@@ -27415,7 +27407,7 @@
       <c r="T57" s="111"/>
       <c r="U57" s="111"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21">
       <c r="A58" s="111"/>
       <c r="B58" s="111"/>
       <c r="C58" s="111"/>
@@ -27427,20 +27419,20 @@
       <c r="I58" s="111"/>
       <c r="J58" s="111"/>
       <c r="K58" s="111"/>
-      <c r="L58" s="218" t="s">
+      <c r="L58" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="M58" s="219"/>
-      <c r="N58" s="219"/>
-      <c r="O58" s="219"/>
-      <c r="P58" s="219"/>
-      <c r="Q58" s="219"/>
-      <c r="R58" s="219"/>
-      <c r="S58" s="219"/>
-      <c r="T58" s="219"/>
-      <c r="U58" s="219"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M58" s="207"/>
+      <c r="N58" s="207"/>
+      <c r="O58" s="207"/>
+      <c r="P58" s="207"/>
+      <c r="Q58" s="207"/>
+      <c r="R58" s="207"/>
+      <c r="S58" s="207"/>
+      <c r="T58" s="207"/>
+      <c r="U58" s="207"/>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" s="111"/>
       <c r="B59" s="111"/>
       <c r="C59" s="111"/>
@@ -27463,12 +27455,12 @@
       <c r="T59" s="130"/>
       <c r="U59" s="130"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="204" t="s">
+    <row r="60" spans="1:21">
+      <c r="A60" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="B60" s="205"/>
-      <c r="C60" s="206"/>
+      <c r="B60" s="197"/>
+      <c r="C60" s="198"/>
       <c r="D60" s="49"/>
       <c r="E60" s="84">
         <v>48520</v>
@@ -27476,15 +27468,15 @@
       <c r="F60" s="71">
         <v>0.318</v>
       </c>
-      <c r="G60" s="207">
+      <c r="G60" s="199">
         <f>E60*0.318</f>
         <v>15429.36</v>
       </c>
-      <c r="H60" s="208"/>
-      <c r="I60" s="209">
+      <c r="H60" s="200"/>
+      <c r="I60" s="201">
         <v>15</v>
       </c>
-      <c r="J60" s="210"/>
+      <c r="J60" s="202"/>
       <c r="K60" s="111"/>
       <c r="L60" s="70"/>
       <c r="M60" s="70"/>
@@ -27497,10 +27489,10 @@
       <c r="T60" s="70"/>
       <c r="U60" s="70"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="204"/>
-      <c r="B61" s="205"/>
-      <c r="C61" s="206"/>
+    <row r="61" spans="1:21">
+      <c r="A61" s="196"/>
+      <c r="B61" s="197"/>
+      <c r="C61" s="198"/>
       <c r="D61" s="49"/>
       <c r="E61" s="84">
         <v>20110</v>
@@ -27508,15 +27500,15 @@
       <c r="F61" s="71">
         <v>0.318</v>
       </c>
-      <c r="G61" s="207">
+      <c r="G61" s="199">
         <f>E61*0.318</f>
         <v>6394.9800000000005</v>
       </c>
-      <c r="H61" s="208"/>
-      <c r="I61" s="209">
+      <c r="H61" s="200"/>
+      <c r="I61" s="201">
         <v>6</v>
       </c>
-      <c r="J61" s="210"/>
+      <c r="J61" s="202"/>
       <c r="K61" s="111"/>
       <c r="L61" s="70"/>
       <c r="M61" s="70"/>
@@ -27529,20 +27521,20 @@
       <c r="T61" s="70"/>
       <c r="U61" s="70"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="204"/>
-      <c r="B62" s="205"/>
-      <c r="C62" s="206"/>
+    <row r="62" spans="1:21">
+      <c r="A62" s="196"/>
+      <c r="B62" s="197"/>
+      <c r="C62" s="198"/>
       <c r="D62" s="117"/>
       <c r="E62" s="85"/>
       <c r="F62" s="71"/>
-      <c r="G62" s="207">
+      <c r="G62" s="199">
         <f>E62*0</f>
         <v>0</v>
       </c>
-      <c r="H62" s="208"/>
-      <c r="I62" s="209"/>
-      <c r="J62" s="210"/>
+      <c r="H62" s="200"/>
+      <c r="I62" s="201"/>
+      <c r="J62" s="202"/>
       <c r="K62" s="111"/>
       <c r="L62" s="111"/>
       <c r="M62" s="111"/>
@@ -27555,20 +27547,20 @@
       <c r="T62" s="111"/>
       <c r="U62" s="111"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="204"/>
-      <c r="B63" s="205"/>
-      <c r="C63" s="206"/>
+    <row r="63" spans="1:21">
+      <c r="A63" s="196"/>
+      <c r="B63" s="197"/>
+      <c r="C63" s="198"/>
       <c r="D63" s="117"/>
       <c r="E63" s="85"/>
       <c r="F63" s="62"/>
-      <c r="G63" s="207">
+      <c r="G63" s="199">
         <f>E63*0</f>
         <v>0</v>
       </c>
-      <c r="H63" s="208"/>
-      <c r="I63" s="230"/>
-      <c r="J63" s="231"/>
+      <c r="H63" s="200"/>
+      <c r="I63" s="228"/>
+      <c r="J63" s="229"/>
       <c r="K63" s="111"/>
       <c r="L63" s="111"/>
       <c r="M63" s="111"/>
@@ -27581,12 +27573,12 @@
       <c r="T63" s="111"/>
       <c r="U63" s="111"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="213" t="s">
+    <row r="64" spans="1:21">
+      <c r="A64" s="220" t="s">
         <v>29</v>
       </c>
-      <c r="B64" s="214"/>
-      <c r="C64" s="215"/>
+      <c r="B64" s="221"/>
+      <c r="C64" s="222"/>
       <c r="D64" s="50">
         <f>SUM(D60:D63)</f>
         <v>0</v>
@@ -27596,19 +27588,33 @@
         <v>68630</v>
       </c>
       <c r="F64" s="60"/>
-      <c r="G64" s="216">
+      <c r="G64" s="223">
         <f>SUM(G60:G63)</f>
         <v>21824.34</v>
       </c>
-      <c r="H64" s="217"/>
-      <c r="I64" s="213">
+      <c r="H64" s="224"/>
+      <c r="I64" s="220">
         <f>SUM(I60:I63)</f>
         <v>21</v>
       </c>
-      <c r="J64" s="215"/>
+      <c r="J64" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G1:N1"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D54:M54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="L58:U58"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="I61:J61"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="G64:H64"/>
     <mergeCell ref="I64:J64"/>
@@ -27618,20 +27624,6 @@
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="I63:J63"/>
-    <mergeCell ref="L58:U58"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="G1:N1"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D54:M54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
